--- a/input/task_1/input.xlsx
+++ b/input/task_1/input.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="300">
   <si>
     <t>id</t>
   </si>
@@ -40,41 +40,47 @@
     <t>authors</t>
   </si>
   <si>
+    <t>tags</t>
+  </si>
+  <si>
     <t>links</t>
   </si>
   <si>
     <t>professions</t>
   </si>
   <si>
-    <t>Как стать логопедом: обучение, обязанности, зарплата и карьерные перспективы</t>
+    <t>Должностная инструкция пробоотборщика: обязанности и правила отбора</t>
   </si>
   <si>
-    <t>Как стать логопедом</t>
+    <t>Должностные обязанности пробоотборщика: правила и инструкции 2026</t>
   </si>
   <si>
-    <t>kak-stat-logopedom</t>
+    <t>obyazannosti-probootborshchika</t>
   </si>
   <si>
-    <t>Узнайте, какое образование необходимо логопеду, где можно работать, сколько зарабатывают специалисты и как построить карьеру.</t>
+    <t>Обязанности пробоотборщика на производстве. Как правильно отбирать пробы, маркировать их и соблюдать технику безопасности.</t>
   </si>
   <si>
-    <t>логопед</t>
+    <t>пробоотборщик обязанности</t>
   </si>
   <si>
-    <t>https://niidpo.ru/blog/s-chego-nachat-kareru-logopeda-praktika-stazhirovki-i-pervye-shagi-v-professii</t>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-probootborshchika/</t>
   </si>
   <si>
-    <t>Педагогика и образование</t>
+    <t>Лаборатории, метрология и качество</t>
   </si>
   <si>
-    <t>Сергей Александрович Николаев; Артём Ильич Афанасьев</t>
+    <t>Григорий Артёмович Назаров, Софья Евгеньевна Максимова, Артём Ильич Афанасьев</t>
+  </si>
+  <si>
+    <t>Пробоотборщик, Обучение рабочим профессиям, Должностные обязанности</t>
   </si>
   <si>
     <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/logoped-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/logoped-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/uchitel-defektolog-distancionnoe-obuchenie/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-laborant-po-analizu-formovochnyh-i-shihtovyh-smesej/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-laborant-probirnogo-analiza/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-himika/
 </t>
     </r>
     <r>
@@ -82,38 +88,52 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/obuchenie/logoped-defektolog-distancionnoe-obuchenie/</t>
+      <t>https://dpoprof.ru/povyshenie/laborant-povyshenie-kvalifikacii/</t>
     </r>
   </si>
   <si>
-    <t>Учитель-дефектолог; Педагог-психолог; Воспитатель; Учитель начальных классов</t>
+    <t>пробоотборщик, лаборант, химик, метролог, анализ</t>
   </si>
   <si>
-    <t>Как стать инструктором по физической культуре в дошкольном образовательном учреждении: обучение и карьера</t>
+    <t>Сестра-хозяйка в больнице: обязанности и требования к должности</t>
   </si>
   <si>
-    <t>Как стать инструктором по физической культуре в дошкольном образовательном учреждении</t>
+    <t>Обязанности сестры-хозяйки в медучреждении: полный обзор</t>
   </si>
   <si>
-    <t>kak-stat-instruktorom-po-fizicheskoy-kulture-v-doshkolnom-obrazovatelnom-uchrezhdenii</t>
+    <t>obyazannosti-sestry-khozyayki</t>
   </si>
   <si>
-    <t>Разбираем профессию инструктора по физической культуре в ДОУ, требования к образованию, обязанности и уровень заработной платы.</t>
+    <t>Что делает сестра-хозяйка? Должностные обязанности, управление младшим персоналом и обеспечение отделения всем необходимым.</t>
   </si>
   <si>
-    <t>инструктор по физической культуре в ДОУ</t>
+    <t>сестра хозяйка обязанности</t>
   </si>
   <si>
-    <t>https://niidpo.ru/blog/professiya-instruktor-po-fizicheskoj-kulture-v-doshkolnom-obrazovatelnom-uchrezhdenii</t>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-sestry-hozyajki/</t>
   </si>
   <si>
-    <t>Денис Валерьевич Громов; Глеб Романович Ларионов</t>
+    <t>Медицина и здравоохранение</t>
+  </si>
+  <si>
+    <t>Дарья Геннадьевна Власьева, Артём Ильич Афанасьев, Алёна Дмитриевна Богомолова</t>
+  </si>
+  <si>
+    <t>Сестра-хозяйка, Обучение медперсонала, Должностные обязанности</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie-medpersonala/medicinskaja-sestra-v-hirurgii-distancionnoe-obuchenie/
+</t>
+    </r>
+    <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie-medpersonala/instruktor-po-lfk-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/instruktor-po-sportu-obuchenie-s-vneseniem-v-frdo/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie-medpersonala/hirurgicheskaja-medsestra-distancionnoe-obuchenie/
+https://dpoprof.ru/obuchenie-medpersonala/prakticheskaja-medsestra-distancionnoe-obuchenie/
 </t>
     </r>
     <r>
@@ -121,407 +141,81 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/perepodgotovka/sport-distancionnaja-perepodgotovka/</t>
+      <t>https://dpoprof.ru/obuchenie-medpersonala/medicinskaja-sestra-distancionnoe-obuchenie/</t>
     </r>
   </si>
   <si>
-    <t>Воспитатель детского сада; Инструктор ЛФК; Учитель физической культуры; Тренер-преподаватель</t>
+    <t>сестра-хозяйка, санитар, медсестра, завхоз, больница</t>
   </si>
   <si>
-    <t>Как стать учителем начальных классов: образование, обязанности и зарплата</t>
+    <t>Обязанности оператора товарного на нефтебазе и АЗС</t>
   </si>
   <si>
-    <t>Как стать учителем начальных классов</t>
+    <t>Обязанности оператора товарного: работа на нефтебазах и складах</t>
   </si>
   <si>
-    <t>kak-stat-uchitelem-nachalnykh-klassov</t>
+    <t>obyazannosti-operatora-tovarnogo</t>
   </si>
   <si>
-    <t>Кто может работать учителем начальных классов, какое образование требуется и какие перспективы доступны специалистам.</t>
+    <t>Должностные обязанности товарного оператора. Прием и отпуск нефтепродуктов, замеры резервуаров и ведение отчетности.</t>
   </si>
   <si>
-    <t>учитель начальных классов</t>
+    <t>оператор товарный обязанности</t>
   </si>
   <si>
-    <t>https://niidpo.ru/blog/professiya-uchitel-nachalnykh-klassov-obyazannosti-chto-nuzhno-delat-i-skolko-mozhno-zarabatyvat</t>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-operatora-tovarnogo/</t>
   </si>
   <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/uchitel-nachalnyh-klassov-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/uchitel-defektolog-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/vospitatel-detskogo-sada-distancionnoe-obuchenie/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://dpoprof.ru/perepodgotovka/pedagog-distancionnaja-perepodgotovka/</t>
-    </r>
+    <t>Добыча и переработка ресурсов</t>
   </si>
   <si>
-    <t>Учитель русского языка; Воспитатель; Педагог дополнительного образования; Социальный педагог</t>
+    <t>Эдуард Николаевич Исаев, Павел Сергеевич Григорьев, Артём Ильич Афанасьев</t>
   </si>
   <si>
-    <t>Как стать учителем физкультуры: обучение, обязанности и карьерные перспективы</t>
+    <t>Оператор товарный, Обучение рабочим профессиям, Должностные обязанности</t>
   </si>
   <si>
-    <t>Как стать учителем физкультуры</t>
+    <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-operator-tovarnyj/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-operator/
+https://dpoprof.ru/povyshenie/povyshenie-kvalifikaczii-operatorov/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-operator-shvejnogo-oborudovaniya/</t>
   </si>
   <si>
-    <t>kak-stat-uchitelem-fizkultury</t>
+    <t>оператор, нефтебаза, резервуар, кладовщик, нефтепродукты</t>
   </si>
   <si>
-    <t>Узнайте, какое образование необходимо учителю физкультуры, где работать и сколько можно зарабатывать в профессии.</t>
+    <t>Должностные обязанности кассира-операциониста: инструкции и функции</t>
   </si>
   <si>
-    <t>учитель физкультуры</t>
+    <t>Обязанности кассира-операциониста: работа с деньгами и клиентами</t>
   </si>
   <si>
-    <t>https://niidpo.ru/blog/professiya-uchitel-fizkultury-kak-im-stat-skolko-mozhno-zarabatyvat</t>
+    <t>obyazannosti-kassira-operatsionista</t>
   </si>
   <si>
-    <t>Денис Валерьевич Громов; Сергей Александрович Николаев</t>
+    <t>Что входит в обязанности кассира-операциониста? Ведение кассовой дисциплины, валютные операции и правила общения с клиентами.</t>
   </si>
   <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/uchitel-prava-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/uchitel-obshhestvoznanija-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/uchitel-istorii-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/uchitel-russkogo-jazyka-i-literatury-distancionnoe-obuchenie/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://dpoprof.ru/obuchenie/uchitel-nachalnyh-klassov-distancionnoe-obuchenie/</t>
-    </r>
+    <t>кассир операционист обязанности</t>
   </si>
   <si>
-    <t>Тренер-преподаватель; Инструктор по спорту; Учитель ОБЖ; Инструктор ЛФК</t>
-  </si>
-  <si>
-    <t>Как успешно сдать тесты по клиническим рекомендациям: руководство для медицинских специалистов</t>
-  </si>
-  <si>
-    <t>Как успешно сдать тесты по клиническим рекомендациям</t>
-  </si>
-  <si>
-    <t>kak-uspeshno-sdat-testy-po-klinicheskim-rekomendatsiyam</t>
-  </si>
-  <si>
-    <t>Полезные рекомендации по подготовке к тестированию по клиническим рекомендациям для медицинских работников.</t>
-  </si>
-  <si>
-    <t>тесты по клиническим рекомендациям</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/mediczina/kak-uspeshno-sdat-testyi-po-klinicheskim-rekomendacziyam-sovetyi-i-resursyi-dlya-mediczinskix-speczialistov2/</t>
-  </si>
-  <si>
-    <t>Медицина и здравоохранение</t>
-  </si>
-  <si>
-    <t>Дарья Геннадьевна Власьева; Артём Ильич Афанасьев</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie-medpersonala/feldsher-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie-medpersonala/medicinskaja-sestra-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/obuchenie-skoroj-medicinskoj-pomoshhi/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://dpoprof.ru/obuchenie-medpersonala/operacionnaja-medicinskaja-sestra-distancionnoe-obuchenie/</t>
-    </r>
-  </si>
-  <si>
-    <t>Врач; Медицинская сестра; Фельдшер; Врач общей практики</t>
-  </si>
-  <si>
-    <t>Профессия фармаколог: кто это, чем занимается, как стать и сколько зарабатывает</t>
-  </si>
-  <si>
-    <t>Профессия фармаколог</t>
-  </si>
-  <si>
-    <t>professiya-farmakolog</t>
-  </si>
-  <si>
-    <t>Кто такой фармаколог, какое образование необходимо получить, чем занимается специалист и какие карьерные перспективы доступны.</t>
-  </si>
-  <si>
-    <t>фармаколог</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/mediczina/farmakolog-kto-eto-kak-stat-chem-zanimaetsya/</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/medpersonal-distancionnoe-obuchenie/
-https://dpoprof.ru/povyshenie/povichenie-kvalificacii-na-medicinu-i-zdorovie/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://dpoprof.ru/obuchenie-medpersonala/farmacevt-distancionnoe-obuchenie/</t>
-    </r>
-  </si>
-  <si>
-    <t>Провизор; Фармацевт; Химик; Биохимик</t>
-  </si>
-  <si>
-    <t>Периодическая аккредитация: как пройти, какие документы подготовить и как подать заявление</t>
-  </si>
-  <si>
-    <t>Периодическая аккредитация медицинских работников</t>
-  </si>
-  <si>
-    <t>periodicheskaya-akkreditatsiya-meditsinskikh-rabotnikov</t>
-  </si>
-  <si>
-    <t>Пошаговая инструкция по прохождению периодической аккредитации, перечень документов и особенности подачи заявления.</t>
-  </si>
-  <si>
-    <t>периодическая аккредитация медицинских работников</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/mediczina/periodicheskaya-akkreditacziya-kak-projti/</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t xml:space="preserve">https://dpoprof.ru/perepodgotovka/medicina-i-zdravoohranenie-distancionnaja-perepodgotovka/
-</t>
-    </r>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/medpersonal-distancionnoe-obuchenie/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://dpoprof.ru/obuchenie-medpersonala/medicinskaja-sestra-v-terapii-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie-medpersonala/administrator-medicinskogo-centra-distancionnoe-obuchenie/</t>
-    </r>
-  </si>
-  <si>
-    <t>Врач; Медицинская сестра; Фельдшер; Специалист по медицинскому образованию</t>
-  </si>
-  <si>
-    <t>Профессия врач-диетолог: кто это, чем занимается, как стать и сколько зарабатывает</t>
-  </si>
-  <si>
-    <t>Профессия врач-диетолог</t>
-  </si>
-  <si>
-    <t>professiya-vrach-dietolog</t>
-  </si>
-  <si>
-    <t>Узнайте, чем занимается врач-диетолог, какие заболевания помогает корректировать и какое образование требуется для профессии.</t>
-  </si>
-  <si>
-    <t>врач-диетолог</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/mediczina/vrach-dietolog-kto-eto/</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie-medpersonala/dietolog-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie-medpersonala/vrach-pediatr-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie-medpersonala/vrach-obshhej-praktiki-distancionnoe-obuchenie/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://dpoprof.ru/obuchenie/povar-dietolog-dieticheskoe-pitanie/</t>
-    </r>
-  </si>
-  <si>
-    <t>Врач-эндокринолог; Нутрициолог; Терапевт; Гастроэнтеролог</t>
-  </si>
-  <si>
-    <t>Профессия клинический биоинформатик: кто это, чем занимается и как стать специалистом</t>
-  </si>
-  <si>
-    <t>Профессия клинический биоинформатик</t>
-  </si>
-  <si>
-    <t>professiya-klinicheskiy-bioinformatik</t>
-  </si>
-  <si>
-    <t>Разбираем профессию клинического биоинформатика, требования к образованию, обязанности и перспективы развития.</t>
-  </si>
-  <si>
-    <t>клинический биоинформатик</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/mediczina/klinicheskij-bioinformatik-kto-eto/</t>
-  </si>
-  <si>
-    <t>Максим Анатольевич Чернов; Дарья Геннадьевна Власьева</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-mikrobiologa/
-</t>
-    </r>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/povyshenie/povyshenie-kvalifikacii-biotehnologii-biologicheski-aktivnyh-veshhestv/
-https://dpoprof.ru/perepodgotovka/distancionnaya-perepodgotovka-laborant-stroitelnoj-laboratorii/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://dpoprof.ru/obuchenie-medpersonala/laborant-kliniko-diagnosticheskoj-laboratorii-distancionnoe-obuchenie/</t>
-    </r>
-  </si>
-  <si>
-    <t>Биоинформатик; Биотехнолог; Программист; Специалист по анализу данных</t>
-  </si>
-  <si>
-    <t>Профессия врач клинической лабораторной диагностики: обязанности, обучение и зарплата</t>
-  </si>
-  <si>
-    <t>Профессия врач клинической лабораторной диагностики</t>
-  </si>
-  <si>
-    <t>professiya-vrach-klinicheskoy-laboratornoy-diagnostiki</t>
-  </si>
-  <si>
-    <t>Кто такой врач КЛД, чем занимается, какое образование необходимо получить и сколько зарабатывают специалисты.</t>
-  </si>
-  <si>
-    <t>врач клинической лабораторной диагностики</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/mediczina/vrach-klinicheskoj-laboratornoj-diagnostiki-kto-eto/</t>
-  </si>
-  <si>
-    <t>Григорий Артёмович Назаров; Дарья Геннадьевна Власьева</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie-medpersonala/laborant-kliniko-diagnosticheskoj-laboratorii-distancionnoe-obuchenie/
-https://dpoprof.ru/perepodgotovka/defektoskopist/
-https://dpoprof.ru/obuchenie-medpersonala/vrach-ultrazvukovoj-diagnostiki-distancionnoe-obuchenie/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://dpoprof.ru/obuchenie-medpersonala/rentgenolaborant-distancionnoe-obuchenie/</t>
-    </r>
-  </si>
-  <si>
-    <t>Лаборант; Врач-бактериолог; Врач-эпидемиолог; Биолог</t>
-  </si>
-  <si>
-    <t>Как стать руководителем: обучение, обязанности, навыки и карьерный рост</t>
-  </si>
-  <si>
-    <t>Как стать руководителем: обучение, обязанности и карьерные перспективы</t>
-  </si>
-  <si>
-    <t>kak-stat-rukovoditelem-obuchenie-obyazannosti-i-karernye-perspektivy</t>
-  </si>
-  <si>
-    <t>Кто такой руководитель, чем занимается, какие обязанности выполняет, где пройти обучение и какие навыки необходимы для успешного управления командой.</t>
-  </si>
-  <si>
-    <t>как стать руководителем</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/buxgalteriya-ekonomika-finansyi/rukovoditel-kto-eto-chto-delaet/</t>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-kassira-operacionista/</t>
   </si>
   <si>
     <t>Финансы, право и управление</t>
   </si>
   <si>
-    <t>Константин Аркадьевич Ветров; Артём Ильич Афанасьев</t>
+    <t>Алёна Дмитриевна Богомолова, Артём Ильич Афанасьев, Тимур Эдуардович Рахманов</t>
+  </si>
+  <si>
+    <t>Кассир-операционист, Переподготовка, Должностные обязанности</t>
   </si>
   <si>
     <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-upravlenie-proektami/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-upravlenie-i-administrirovanie/
-https://dpoprof.ru/obuchenie/obuchenie-upravleniju-personalom/
-https://dpoprof.ru/obuchenie/upravlenie-v-sfere-obrazovanija-distancionnoe-obuchenie/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-slozhnye-voprosy-v-rabote-kadrovoj-sluzhby-i-effektivnaya-sistema-upravleniem-personalom-v-organizacii/</t>
-    </r>
-  </si>
-  <si>
-    <t>Руководитель отдела; Менеджер проекта; Директор; Исполнительный директор</t>
-  </si>
-  <si>
-    <t>Как стать экономистом на предприятии: обязанности, навыки, зарплата и перспективы</t>
-  </si>
-  <si>
-    <t>Экономист на предприятии: обязанности, навыки и перспективы профессии</t>
-  </si>
-  <si>
-    <t>ekonomist-na-predpriyatii-obyazannosti-navyki-i-perspektivy-professii</t>
-  </si>
-  <si>
-    <t>Чем занимается экономист на предприятии, какие задачи решает, сколько зарабатывает и где получить образование для работы по профессии.</t>
-  </si>
-  <si>
-    <t>экономист на предприятии</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/buxgalteriya-ekonomika-finansyi/chem-zanimaetsya-ekonomist-na-predpriyatii/</t>
-  </si>
-  <si>
-    <t>Алёна Дмитриевна Богомолова; Константин Аркадьевич Ветров</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-ekonomiku-i-upravlenie/
-https://dpoprof.ru/povyshenie/povishenie-kvalificacii-smetshik/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-kassira/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-bankovskomu-delu/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-prodavca/
 https://dpoprof.ru/perepodgotovka/buhgalter/
 </t>
     </r>
@@ -530,36 +224,42 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/perepodgotovka/bankovskoe-delo/</t>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-buhgalterskij-uchet-analiz-i-audit/</t>
     </r>
   </si>
   <si>
-    <t>Бухгалтер; Финансовый аналитик; Аудитор; Экономист по труду</t>
+    <t>кассир, операционист, бухгалтер, оператор, банк</t>
   </si>
   <si>
-    <t>Как стать оценщиком бизнеса: кто это, как стать, обязанности и уровень дохода</t>
+    <t>Профессия горнорабочий: обязанности в шахте и на поверхности</t>
   </si>
   <si>
-    <t>Оценщик бизнеса: как стать специалистом и сколько можно зарабатывать</t>
+    <t>Обязанности горнорабочего: специфика работы и требования</t>
   </si>
   <si>
-    <t>otsenshchik-biznesa-kak-stat-spetsialistom-i-skolko-mozhno-zarabatyvat</t>
+    <t>obyazannosti-gornorabochego</t>
   </si>
   <si>
-    <t>Разбираем профессию оценщика бизнеса: чем занимается специалист, какое образование необходимо и сколько можно зарабатывать.</t>
+    <t>Должностные обязанности горнорабочего. Виды работ, требования к физической подготовке, охрана труда и подземный стаж.</t>
   </si>
   <si>
-    <t>оценщик бизнеса</t>
+    <t>горнорабочий обязанности</t>
   </si>
   <si>
-    <t>https://cpkedu.ru/novosti/buxgalteriya-ekonomika-finansyi/oczenshhik-biznesa-kto-eto-chto-delaet/</t>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-gornorabochego/</t>
+  </si>
+  <si>
+    <t>Эдуард Николаевич Исаев, Артём Ильич Афанасьев, Юрий Борисович Гончаров</t>
+  </si>
+  <si>
+    <t>Горнорабочий, Обучение рабочим профессиям, Должностные обязанности</t>
   </si>
   <si>
     <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/perepodgotovka/distancionnaya-perepodgotovka-specialist-ocenki-biznesa-dvizhimogo-i-nedvizhimogo-imushestva/
-https://dpoprof.ru/povyshenie/povichenie-kvalificacii-ochenshik/
-https://dpoprof.ru/obuchenie/nedvigimost/
+      <t xml:space="preserve">https://dpoprof.ru/povyshenie/povichenie-kvalificacii-na-gornoraboshego/
+https://dpoprof.ru/perepodgotovka/gornorabochij/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-gornorabochego/
 </t>
     </r>
     <r>
@@ -567,35 +267,94 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-biznes-kouching/</t>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-marksheikerskoe-delo/</t>
     </r>
   </si>
   <si>
-    <t>Аудитор; Финансовый аналитик; Бизнес-консультант; Экономист</t>
+    <t>горнорабочий, шахтер, проходчик, крепильщик, рудник</t>
   </si>
   <si>
-    <t>Как стать энергоаудитором: кто это, как стать специалистом и где пройти обучение</t>
+    <t>Обучение на газосварщика в 2026 году — как получить профессию и начать работать</t>
   </si>
   <si>
-    <t>Энергоаудитор: обязанности, обучение и карьерные возможности</t>
+    <t>Обучение на газосварщика: где пройти курсы и получить профессию</t>
   </si>
   <si>
-    <t>energoauditor-obyazannosti-obuchenie-i-karernye-vozmozhnosti</t>
+    <t>obuchenie-na-gazosvarshchika</t>
   </si>
   <si>
-    <t>Кто такой энергоаудитор, какие проверки проводит, какие требования предъявляются к профессии и как получить необходимые компетенции.</t>
+    <t>Узнайте, как пройти обучение на газосварщика, сколько длится курс и какие навыки получает специалист. Подробно о получении профессии.</t>
   </si>
   <si>
-    <t>энергоаудитор</t>
+    <t>обучение на газосварщика</t>
   </si>
   <si>
-    <t>https://cpkedu.ru/novosti/zhkx/energoauditor-kto-eto-chto-delaet-kak-stat-obuchenie/</t>
+    <t>https://profgid.ru/professii/gazosvarshchik/</t>
   </si>
   <si>
-    <t>Энергетика и электрика</t>
+    <t>Сварка, слесарка и металлообработка</t>
   </si>
   <si>
-    <t>Семён Игоревич Леонов; Артём Ильич Афанасьев</t>
+    <t>Роман Дмитриевич Гордеев, Светлана Руслановна Маслова, Артём Ильич Афанасьев</t>
+  </si>
+  <si>
+    <t>Газосварщик, Обучение рабочим профессиям, Как стать</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/jelektrogazosvarshhik/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-gazosvarshika/
+https://dpoprof.ru/perepodgotovka/slesar-distancionnaja-perepodgotovka/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-elektrogazosvarshik-vrezchik/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/jelektrogazosvarshhik/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-gazosvarshika/
+https://dpoprof.ru/perepodgotovka/slesar-distancionnaja-perepodgotovka/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-elektrogazosvarshik-vrezchik/</t>
+    </r>
+  </si>
+  <si>
+    <t>Профессия газосварщик: обязанности, обучение и зарплата в 2026 году</t>
+  </si>
+  <si>
+    <t>Профессия газосварщик: чем занимается специалист и как им стать</t>
+  </si>
+  <si>
+    <t>professiya-gazosvarshchik</t>
+  </si>
+  <si>
+    <t>Узнайте, чем занимается газосварщик, какие навыки нужны для работы и где пройти обучение. Подробно о профессии и карьерных возможностях.</t>
+  </si>
+  <si>
+    <t>профессия газосварщик</t>
+  </si>
+  <si>
+    <t>https://russia.trud.com/article/gazosvarshchik-professiya/</t>
+  </si>
+  <si>
+    <t>Светлана Руслановна Маслова, Роман Дмитриевич Гордеев, Артём Ильич Афанасьев</t>
+  </si>
+  <si>
+    <t>Газосварщик, Обучение рабочим профессиям, Профессии</t>
   </si>
   <si>
     <r>
@@ -603,13 +362,12 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-energoaudit-zdanij-i-sooruzhenij/
-</t>
+      <t>https://dpoprof.ru/obuchenie/jelektrogazosvarshhik/</t>
     </r>
     <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/povyshenie/povyshenie-kvalifikacii-avtonomnaya-energetika-predpriyatij/
-https://dpoprof.ru/perepodgotovka/distancionnaya-perepodgotovka-energeticheskij-menedzhment-i-energoaudit/
+      <t xml:space="preserve">
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-gazosvarshika/
 </t>
     </r>
     <r>
@@ -617,40 +375,11 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/bezopasnost/ekologicheskaya-bezopasnost/ekologicheskij-audit/</t>
+      <t>https://dpoprof.ru/perepodgotovka/distancionnaya-perepodgotovka-elektrogazosvarshik/</t>
     </r>
-  </si>
-  <si>
-    <t>Инженер-энергетик; Энергетик; Инженер КИПиА; Электромонтер</t>
-  </si>
-  <si>
-    <t>Как стать экоаудитором: кто это, чем занимается и как освоить профессию</t>
-  </si>
-  <si>
-    <t>Экоаудитор: как стать специалистом в сфере экологического аудита</t>
-  </si>
-  <si>
-    <t>ekoauditor-kak-stat-spetsialistom-v-sfere-ekologicheskogo-audita</t>
-  </si>
-  <si>
-    <t>Все о профессии экоаудитора: обязанности, необходимые знания, обучение и перспективы работы в сфере экологического контроля.</t>
-  </si>
-  <si>
-    <t>экоаудитор</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/ekologiya/ekoauditor-kto-eto-chto-delaet-kak-stat/</t>
-  </si>
-  <si>
-    <t>Алёна Дмитриевна Богомолова; Артём Ильич Афанасьев</t>
-  </si>
-  <si>
     <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/bezopasnost/ekologicheskaya-bezopasnost/ekologicheskij-audit/
-https://dpoprof.ru/bezopasnost/ekologicheskaya-bezopasnost/ekologicheskaya-bezopasnost-v-stroitelstve/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-ekologiu/
-https://dpoprof.ru/obuchenie/obuchenie-po-jekologii-i-ohrane-okruzhajushhej-sredy/
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -658,39 +387,39 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/bezopasnost/ekologicheskaya-bezopasnost/ekologicheskaya-bezopasnost-obrashheniya-s-othodami/</t>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-elektrogazosvarshik-vrezchik/</t>
     </r>
   </si>
   <si>
-    <t>Эколог; Специалист по охране окружающей среды; Аудитор; Инженер по охране труда</t>
+    <t>газосварщик, сварщик, газорезчик, монтажник, слесарь</t>
   </si>
   <si>
-    <t>Как стать персональным тренером: обязанности, обучение и перспективы профессии</t>
+    <t>Разряды газосварщиков: категории, обязанности и зарплата в 2026 году</t>
   </si>
   <si>
-    <t>Персональный тренер: как стать специалистом и развиваться в профессии</t>
+    <t>Разряды газосварщиков: какие бывают и чем отличаются</t>
   </si>
   <si>
-    <t>personalnyy-trener-kak-stat-spetsialistom-i-razvivatsya-v-professii</t>
+    <t>razryady-gazosvarshchikov</t>
   </si>
   <si>
-    <t>Чем занимается персональный тренер, какие навыки необходимы для работы, как пройти обучение и начать карьеру.</t>
+    <t>Разряды газосварщиков: какие категории существуют, чем отличаются обязанности и какая зарплата у специалистов разных разрядов.</t>
   </si>
   <si>
-    <t>персональный тренер</t>
+    <t>разряды газосварщиков</t>
   </si>
   <si>
-    <t>https://cpkedu.ru/novosti/fizicheskaya-kultura-i-sport/personalnyij-trener-kto-eto-chto-delaet-kak-stat/</t>
+    <t>https://profobrazovanie.org/gazosvarshchik/</t>
   </si>
   <si>
-    <t>Денис Валерьевич Громов; Артём Ильич Афанасьев</t>
+    <t>Газосварщик, Повышение квалификации, Квалификационные разряды</t>
   </si>
   <si>
     <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie-medpersonala/instruktor-po-lfk-distancionnoe-obuchenie/
-https://dpoprof.ru/perepodgotovka/sport-distancionnaja-perepodgotovka/
-https://dpoprof.ru/obuchenie/uchitel-fizicheskoj-kultury-distancionnoe-obuchenie/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/jelektrogazosvarshhik/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-gazosvarshika/
+https://dpoprof.ru/perepodgotovka/slesar-distancionnaja-perepodgotovka/
 </t>
     </r>
     <r>
@@ -698,66 +427,52 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/obuchenie/instruktor-po-sportu-obuchenie-s-vneseniem-v-frdo/</t>
+      <t>https://dpoprof.ru/perepodgotovka/gazosvarshhik//</t>
     </r>
   </si>
   <si>
-    <t>Фитнес-тренер; Инструктор тренажерного зала; Тренер ЛФК; Инструктор по спорту</t>
+    <t>газосварщик, сварщик, разряд, квалификация, газорезчик</t>
   </si>
   <si>
-    <t>Как стать HR-менеджером: обучение, обязанности и карьерный рост</t>
+    <t>Обучение на сантехника в 2026 году — как получить профессию и начать работать</t>
   </si>
   <si>
-    <t>Как стать HR-менеджером и построить карьеру в управлении персоналом</t>
+    <t>Обучение на сантехника: где пройти курсы и получить профессию</t>
   </si>
   <si>
-    <t>kak-stat-hr-menedzherom-i-postroit-kareru-v-upravlenii-personalom</t>
+    <t>obuchenie-na-santekhnika</t>
   </si>
   <si>
-    <t>Кто такой HR-менеджер, какие задачи выполняет, где пройти обучение и как построить карьеру в сфере управления персоналом.</t>
+    <t>Узнайте, как пройти обучение на сантехника, какие навыки нужно освоить и сколько длится курс. Подробно о получении профессии сантехника.</t>
   </si>
   <si>
-    <t>как стать HR-менеджером</t>
+    <t>обучение на сантехника</t>
   </si>
   <si>
-    <t>https://cpkedu.ru/novosti/novosti-industrii/kak-stat-HR-menedzherom-i-razvivatsya-v-upravlenii-personalom/</t>
+    <t>https://professii-online.ru/gazosvarshchik/</t>
   </si>
   <si>
-    <t>Константин Аркадьевич Ветров; Алёна Дмитриевна Богомолова</t>
+    <t>ЖКХ, отопление и инженерные системы</t>
   </si>
   <si>
-    <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-upravlenie-i-hr/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-slozhnye-voprosy-v-rabote-kadrovoj-sluzhby-i-effektivnaya-sistema-upravleniem-personalom-v-organizacii/
-https://dpoprof.ru/perepodgotovka/upravlenie-personalom-i-hr-distancionnaja-perepodgotovka/
-</t>
+    <t>Вячеслав Борисович Воинов, Станислав Николаевич Попов, Артём Ильич Афанасьев</t>
   </si>
   <si>
-    <t>Рекрутер; Менеджер по персоналу; HR Business Partner; Специалист по кадровому делопроизводству</t>
-  </si>
-  <si>
-    <t>Как стать тренером по йоге и пилатесу: обязанности, обучение и перспективы профессии</t>
-  </si>
-  <si>
-    <t>Тренер по йоге и пилатесу: обязанности и карьерные перспективы</t>
-  </si>
-  <si>
-    <t>trener-po-yoge-i-pilatesu-obyazannosti-i-karernye-perspektivy</t>
-  </si>
-  <si>
-    <t>Чем занимается тренер по йоге и пилатесу, какие навыки необходимы для работы и как начать карьеру в сфере фитнеса.</t>
-  </si>
-  <si>
-    <t>тренер по йоге и пилатесу</t>
-  </si>
-  <si>
-    <t>https://cpkedu.ru/novosti/novosti-industrii/trener-po-joge-i-pilatesu-kto-eto,-obyazannosti-i-perspektivyi/</t>
+    <t>Сантехник, Обучение рабочим профессиям, Как стать</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-santehnik/
+</t>
+    </r>
+    <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/perepodgotovka/sport-distancionnaja-perepodgotovka/
-https://dpoprof.ru/povyshenie/instruktor-po-sportu-distancionnoe-povyshenie-kvalifikacii-s-vneseniem-v-frd/
-https://dpoprof.ru/obuchenie-medpersonala/instruktor-po-lfk-distancionnoe-obuchenie/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-slesar-santehnik/
+https://dpoprof.ru/perepodgotovka/santehnik-perepodgotovka/
 </t>
     </r>
     <r>
@@ -765,77 +480,49 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/obuchenie/uchitel-fizicheskoj-kultury-distancionnoe-obuchenie/</t>
+      <t>https://dpoprof.ru/perepodgotovka/slesar-distancionnaja-perepodgotovka/</t>
     </r>
   </si>
   <si>
-    <t>Фитнес-тренер; Инструктор групповых программ; Инструктор по стретчингу; Инструктор ЛФК</t>
+    <t>сантехник, слесарь, монтажник, трубопроводчик, водопроводчик</t>
   </si>
   <si>
-    <t>Как стать специалистом 1С: кто это, чем занимается и как начать карьеру</t>
+    <t>Профессия сантехник: обязанности, навыки и зарплата в 2026 году</t>
   </si>
   <si>
-    <t>Специалист 1С: как стать востребованным экспертом</t>
+    <t>Профессия сантехник: чем занимается специалист и как им стать</t>
   </si>
   <si>
-    <t>spetsialist-1s-kak-stat-vostrebovannym-ekspertom</t>
+    <t>professiya-santekhnik</t>
   </si>
   <si>
-    <t>Разбираем профессию специалиста 1С: обязанности, востребованные навыки, обучение и возможности трудоустройства.</t>
+    <t>Узнайте, чем занимается сантехник, какие навыки нужны для работы и где пройти обучение. Полное руководство по профессии и карьерным возможностям.</t>
   </si>
   <si>
-    <t>специалист 1С</t>
+    <t>профессия сантехник</t>
   </si>
   <si>
-    <t>https://cpkedu.ru/novosti/buxgalteriya-ekonomika-finansyi/speczialist-1s-kto-eto/</t>
+    <t>https://profi.ru/blog/kak-stat-santehnikom/</t>
   </si>
   <si>
-    <t>IT и цифровые профессии</t>
+    <t>Вячеслав Борисович Воинов, Артём Ильич Афанасьев, Станислав Николаевич Попов</t>
   </si>
   <si>
-    <t>Максим Анатольевич Чернов; Алёна Дмитриевна Богомолова</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-programmirovanie/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-informatika-i-vychislitelnaya-tehnika/
-https://dpoprof.ru/perepodgotovka/programmirovanie/
-https://dpoprof.ru/obuchenie/prepodavatel-robototehniki-distancionnoe-obuchenie/
-</t>
-  </si>
-  <si>
-    <t>Программист 1С; Системный аналитик; Консультант 1С; Разработчик ERP</t>
-  </si>
-  <si>
-    <t>Смена профессии в 40 лет: как начать новую карьеру и выбрать направление</t>
-  </si>
-  <si>
-    <t>Смена профессии в 40 лет: пошаговый план перехода в новую сферу</t>
-  </si>
-  <si>
-    <t>smena-professii-v-40-let-poshagovyy-plan-perekhoda-v-novuyu-sferu</t>
-  </si>
-  <si>
-    <t>Реально ли сменить профессию после 40 лет, какие специальности востребованы и как пройти обучение для нового старта.</t>
-  </si>
-  <si>
-    <t>смена профессии в 40 лет</t>
-  </si>
-  <si>
-    <t>https://centrfenix.ru/articles/smena-professii-v-40-let-s-chego-nachat-i-kakie-napravleniya-rassmotret-/</t>
-  </si>
-  <si>
-    <t>Редакция и общие темы</t>
-  </si>
-  <si>
-    <t>Артём Ильич Афанасьев; Константин Аркадьевич Ветров</t>
+    <t>Сантехник, Обучение рабочим профессиям, Профессии</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-santehnik/
+</t>
+    </r>
+    <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/bezopasnost/ohrana-truda/obuchenie-po-ohrane-truda-i-proverki-znanij/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-elektromontazhnik-shemshik/
-https://dpoprof.ru/obuchenie/operator-stanka-chpu-obuchenie/
-https://dpoprof.ru/obuchenie/kladovshhik-distancionnoe-obuchenie/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-slesar-santehnik/
+https://dpoprof.ru/perepodgotovka/santehnik-perepodgotovka/
 </t>
     </r>
     <r>
@@ -843,42 +530,46 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-operator/</t>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-montazhnik/</t>
     </r>
   </si>
   <si>
-    <t>Карьерный консультант; HR-менеджер; Профориентолог; Коуч</t>
+    <t>сантехник, слесарь, монтажник, трубопроводчик, мастер</t>
   </si>
   <si>
-    <t>Перенос НОК на 5 лет: можно ли отсрочить независимую оценку квалификации</t>
+    <t>Разряды сантехника: категории, обязанности и зарплата в 2026 году</t>
   </si>
   <si>
-    <t>Можно ли перенести независимую оценку квалификации на 5 лет</t>
+    <t>Разряды сантехника: какие бывают и чем отличаются</t>
   </si>
   <si>
-    <t>mozhno-li-perenesti-nezavisimuyu-otsenku-kvalifikatsii-na-5-let</t>
+    <t>razryady-santekhnika</t>
   </si>
   <si>
-    <t>Разбираем, в каких случаях допускается перенос независимой оценки квалификации, какие требования действуют и как оформить отсрочку.</t>
+    <t>Разряды сантехника: какие категории существуют, чем отличаются обязанности и какая зарплата у специалистов разных разрядов.</t>
   </si>
   <si>
-    <t>перенос независимой оценки квалификации</t>
+    <t>разряды сантехника</t>
   </si>
   <si>
-    <t>https://centrfenix.ru/articles/mozhno_li_spetsialistam_perenesti_na_5_let_nezavisimuyu_otsenku_kvalifikatsii_i_kak_eto_sdelat_zakon/</t>
+    <t>https://www.kp.ru/edu/rabota/professiya-santekhnik/</t>
   </si>
   <si>
-    <t>Новости</t>
-  </si>
-  <si>
-    <t>Тимур Эдуардович Рахманов; Артём Ильич Афанасьев</t>
+    <t>Сантехник, Повышение квалификации, Квалификационные разряды</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-santehnik/
+</t>
+    </r>
+    <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-slesar-elektromontazhnik/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-elektromontazhnik/
-https://dpoprof.ru/obuchenie/montazhnik-sistem-ventiljacii-i-kondicionirovanija/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-slesar-santehnik/
+https://dpoprof.ru/perepodgotovka/santehnik-perepodgotovka/
 </t>
     </r>
     <r>
@@ -886,12 +577,43 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/montazhnik-vysotnye-raboty/
-</t>
+      <t>https://dpoprof.ru/perepodgotovka/slesar-distancionnaja-perepodgotovka/</t>
     </r>
+  </si>
+  <si>
+    <t>сантехник, разряд, квалификация, слесарь, монтажник</t>
+  </si>
+  <si>
+    <t>Как освоить работу маляра в 2026 году – полный курс</t>
+  </si>
+  <si>
+    <t>Освоение работы маляра в 2026 году – полный курс</t>
+  </si>
+  <si>
+    <t>professiya-malyar</t>
+  </si>
+  <si>
+    <t>Освоение работы маляра в 2026 году: обучение и практика под ключ. Советы эксперта помогут быстро освоить профессию.</t>
+  </si>
+  <si>
+    <t>профессия маляр</t>
+  </si>
+  <si>
+    <t>https://profguide.ru/professions/santehnik/</t>
+  </si>
+  <si>
+    <t>Строительство</t>
+  </si>
+  <si>
+    <t>Станислав Николаевич Попов, Артём Ильич Афанасьев, Константин Аркадьевич Ветров</t>
+  </si>
+  <si>
+    <t>Маляр, Обучение рабочим профессиям, Как стать</t>
+  </si>
+  <si>
     <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-vyshkomontazhnik-svarshik/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-malyar/
 </t>
     </r>
     <r>
@@ -899,61 +621,493 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-elektroslesarya/</t>
+      <t>https://dpoprof.ru/obuchenie/otdelochnik-distancionnoe-obuchenie/</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">
+https://dpoprof.ru/perepodgotovka/distancionnaya-perepodgotovka-malyar/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-remont-zdanii/</t>
     </r>
   </si>
   <si>
-    <t>Специалист по сертификации; Эксперт по оценке квалификаций; Аудитор; Специалист по стандартизации</t>
+    <t>маляр, отделочник, штукатур, облицовщик, строитель</t>
   </si>
   <si>
-    <t>Профессиональная переподготовка после 35–40 лет: стоит ли менять профессию</t>
+    <t>Обучение на маляра в 2026 году — как получить профессию и начать работать</t>
   </si>
   <si>
-    <t>Профессиональная переподготовка после 35–40 лет: возможности и перспективы</t>
+    <t>Обучение на маляра: где пройти курсы и получить профессию</t>
   </si>
   <si>
-    <t>professionalnaya-perepodgotovka-posle-35-40-let-vozmozhnosti-i-perspektivy</t>
+    <t>obuchenie-na-malyara</t>
   </si>
   <si>
-    <t>Как пройти профессиональную переподготовку после 35–40 лет, выбрать новое направление и сохранить уровень дохода.</t>
+    <t>Узнайте, как пройти обучение на маляра, сколько длится курс и какие навыки получает специалист. Подробно о получении профессии маляра.</t>
   </si>
   <si>
-    <t>профессиональная переподготовка после 40 лет</t>
+    <t>обучение на маляра</t>
   </si>
   <si>
-    <t>https://centrfenix.ru/articles/professionalnaya-perepodgotovka-posle-35-40-let-realno-li-smenit-napravlenie-i-ne-poteryat-v-dokhode/</t>
+    <t>https://www.kp.ru/edu/rabota/professiya-malyar/</t>
   </si>
   <si>
-    <t>https://dpoprof.ru/bezopasnost/ohrana-truda/obuchenie-po-ohrane-truda-i-proverki-znanij/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-upravlenie-proektami/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-elektromontazhnik-shemshik/
-https://dpoprof.ru/obuchenie/operator-stanka-chpu-obuchenie/
-https://dpoprof.ru/obuchenie/kladovshhik-distancionnoe-obuchenie/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-operator/</t>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-malyar/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-shpaklevshika/</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">
+https://dpoprof.ru/perepodgotovka/distancionnaya-perepodgotovka-malyar/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-remont-zdanii/</t>
+    </r>
   </si>
   <si>
-    <t>Карьерный консультант; HR-менеджер; Коуч; Профориентолог</t>
+    <t>Разряды маляра: обязанности, зарплата и виды работ в 2026 году</t>
   </si>
   <si>
-    <t>Системы дистанционного обучения: виды, функции и сферы применения</t>
+    <t>razryady-malyara</t>
   </si>
   <si>
-    <t>Системы дистанционного обучения: классификация и применение</t>
+    <t>Разряды маляра: обязанности, зарплата и виды работ в 2026 году. Полное руководство по квалификации и карьерному росту.</t>
   </si>
   <si>
-    <t>sistemy-distantsionnogo-obucheniya-klassifikatsiya-i-primenenie</t>
+    <t>разряды маляров</t>
   </si>
   <si>
-    <t>Что такое системы дистанционного обучения, какие бывают виды СДО, их возможности и преимущества для образовательных организаций и бизнеса.</t>
+    <t>https://profgid.ru/professii/malyar/</t>
   </si>
   <si>
-    <t>системы дистанционного обучения</t>
+    <t>Маляр, Повышение квалификации, Квалификационные разряды</t>
   </si>
   <si>
-    <t>https://centrfenix.ru/articles/sistemy-distantsionnogo-obucheniya-sdo-klassifikatsiya-funktsii-primenenie/</t>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-malyar/
+https://dpoprof.ru/perepodgotovka/distancionnaya-perepodgotovka-malyar/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/avtomaljar-distancionnoe-obuchenie/</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-remont-zdanii/</t>
+    </r>
   </si>
   <si>
-    <t>Сергей Александрович Николаев; Максим Анатольевич Чернов</t>
+    <t>маляр, разряд, отделочник, штукатур, квалификация</t>
+  </si>
+  <si>
+    <t>Машинист компрессорных установок: функции и обслуживание оборудования</t>
+  </si>
+  <si>
+    <t>Функции машиниста компрессорных установок: эксплуатация и ремонт</t>
+  </si>
+  <si>
+    <t>funktsii-mashinista-kompressornykh-ustanovok</t>
+  </si>
+  <si>
+    <t>Обязанности и функции машиниста компрессорных установок. Контроль давления, обслуживание оборудования и действия в аварийных ситуациях.</t>
+  </si>
+  <si>
+    <t>машинист компрессорных установок функции</t>
+  </si>
+  <si>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-mashinista-kompressornyh-ustanovok/</t>
+  </si>
+  <si>
+    <t>Энергетика и электрика</t>
+  </si>
+  <si>
+    <t>Семён Игоревич Леонов, Павел Сергеевич Григорьев, Артём Ильич Афанасьев</t>
+  </si>
+  <si>
+    <t>Машинист компрессорных установок, Обучение рабочим профессиям, Должностные обязанности</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/perepodgotovka/operator-distancionnaja-perepodgotovka/
+https://dpoprof.ru/obuchenie/mashinist-buldozera-obuchenie-s-vydachej-udostovereniya-ustanovlennogo-obrazcza-v-uchebnom-czentre-professionalnogo-obrazovaniya/
+https://dpoprof.ru/obuchenie/obuchenie-na-traktorista-mashinista/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/obuchenie-na-mashinista-avtomobilnogo-krana/</t>
+    </r>
+  </si>
+  <si>
+    <t>машинист, компрессорщик, оператор, энергетик, механик</t>
+  </si>
+  <si>
+    <t>Мастер строительно-монтажных работ (СМР): обязанности и ответственность</t>
+  </si>
+  <si>
+    <t>Обязанности мастера СМР: управление стройкой и сдача объектов</t>
+  </si>
+  <si>
+    <t>obyazannosti-mastera-smr</t>
+  </si>
+  <si>
+    <t>Должностные обязанности мастера строительно-монтажных работ (СМР). Организация труда бригады, контроль качества и ведение журналов.</t>
+  </si>
+  <si>
+    <t>мастер смр обязанности</t>
+  </si>
+  <si>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-mastera-stroitelno-montazhnyh-rabot/</t>
+  </si>
+  <si>
+    <t>Станислав Николаевич Попов, Константин Аркадьевич Ветров, Артём Ильич Афанасьев</t>
+  </si>
+  <si>
+    <t>Мастер СМР, Переподготовка, Должностные обязанности</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/master/
+https://dpoprof.ru/perepodgotovka/master/
+https://dpoprof.ru/povyshenie/povichenie-kvalificacii-stroitelstvo/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-gilishnoe-stroitelstvo/</t>
+    </r>
+  </si>
+  <si>
+    <t>прораб, мастер, строитель, бригадир, инженер</t>
+  </si>
+  <si>
+    <t>Монтажник слаботочных систем: функции, навыки и специфика работы</t>
+  </si>
+  <si>
+    <t>Функции монтажника слаботочных систем: от прокладки до настройки</t>
+  </si>
+  <si>
+    <t>funktsii-montazhnika-slabotochnykh-sistem</t>
+  </si>
+  <si>
+    <t>Что делает монтажник слаботочных систем? Обязанности по монтажу сигнализации, интернета и видеонаблюдения. Требуемые навыки.</t>
+  </si>
+  <si>
+    <t>монтажник слаботочных систем функции</t>
+  </si>
+  <si>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-montazhnika-slabotochnyh-sistem/</t>
+  </si>
+  <si>
+    <t>Семён Игоревич Леонов, Станислав Николаевич Попов, Артём Ильич Афанасьев</t>
+  </si>
+  <si>
+    <t>Монтажник слаботочных систем, Обучение рабочим профессиям, Должностные обязанности</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/montazhnik-slabotochnyh-sistem/
+https://dpoprof.ru/perepodgotovka/montazhnik-slabotochnyh-sistem/
+https://dpoprof.ru/obuchenie/montazhnik-rea-obuchenie/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-elektromontazhnik-naladchik/</t>
+    </r>
+  </si>
+  <si>
+    <t>монтажник, электромонтажник, связист, инсталлятор, слаботочник</t>
+  </si>
+  <si>
+    <t>Профессия такелажник: обязанности и техника безопасности</t>
+  </si>
+  <si>
+    <t>Обязанности такелажника: правила строповки и перемещения грузов</t>
+  </si>
+  <si>
+    <t>obyazannosti-takelazhnika</t>
+  </si>
+  <si>
+    <t>Должностные обязанности такелажника. Использование подъемных механизмов, выбор строп и строгий контроль техники безопасности.</t>
+  </si>
+  <si>
+    <t>такелажник обязанности</t>
+  </si>
+  <si>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-takelazhnika/</t>
+  </si>
+  <si>
+    <t>Транспорт, спецтехника и логистика</t>
+  </si>
+  <si>
+    <t>Юрий Борисович Гончаров, Артём Ильич Афанасьев, Станислав Николаевич Попов</t>
+  </si>
+  <si>
+    <t>Такелажник, Обучение рабочим профессиям, Должностные обязанности</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-stropalshik/
+https://dpoprof.ru/perepodgotovka/signalist/
+https://dpoprof.ru/perepodgotovka/stropalshhik-perepodgotovka/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/perepodgotovka/distancionnaya-perepodgotovka-mashinist-kranovshik/</t>
+    </r>
+  </si>
+  <si>
+    <t>такелажник, стропальщик, крановщик, грузчик, монтажник</t>
+  </si>
+  <si>
+    <t>Слесарь аварийно-восстановительных работ (АВР): обязанности и задачи</t>
+  </si>
+  <si>
+    <t>Слесарь АВР: обязанности при ликвидации аварий на сетях</t>
+  </si>
+  <si>
+    <t>obyazannosti-slesarya-avr</t>
+  </si>
+  <si>
+    <t>Обязанности слесаря аварийно-восстановительных работ. Устранение порывов, ремонт водопровода и работа в экстренных условиях.</t>
+  </si>
+  <si>
+    <t>слесарь авр обязанности</t>
+  </si>
+  <si>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-slesarya-avarijno-vosstanovitelnyh-rabot-avr/</t>
+  </si>
+  <si>
+    <t>Станислав Николаевич Попов, Вячеслав Борисович Воинов, Артём Ильич Афанасьев</t>
+  </si>
+  <si>
+    <t>Слесарь АВР, Обучение рабочим профессиям, Должностные обязанности</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-vodosnabgeniu-i-vodootvedeniu/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-slesar-santehnik/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-gidroelektrostanciyam/
+</t>
+    </r>
+  </si>
+  <si>
+    <t>слесарь, аварийщик, сантехник, ремонтник, водоканал</t>
+  </si>
+  <si>
+    <t>Слесарь механосборочных работ (МСР): обязанности и разряды</t>
+  </si>
+  <si>
+    <t>Обязанности слесаря МСР: сборка узлов и работа с чертежами</t>
+  </si>
+  <si>
+    <t>obyazannosti-slesarya-msr</t>
+  </si>
+  <si>
+    <t>Что делает слесарь механосборочных работ (МСР)? Обязанности, чтение технической документации и подгонка деталей.</t>
+  </si>
+  <si>
+    <t>слесарь мср обязанности</t>
+  </si>
+  <si>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-slesarya-mekhanosborochnyh-rabot-msr/</t>
+  </si>
+  <si>
+    <t>Артём Станиславович Ерёмин, Станислав Николаевич Попов, Артём Ильич Афанасьев</t>
+  </si>
+  <si>
+    <t>Слесарь МСР, Обучение рабочим профессиям, Должностные обязанности</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/operator-stanka-chpu-obuchenie/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-elektroslesarya/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-slesar-po-izgotovleniyu-i-dovodke-detalej-letatelnyh-apparatov/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-slesar-elektrik-po-obsluzhivaniyu-i-remontu-metallokonstrukcij-metropolitena/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-elektroslesar-po-obsluzhivaniyu-i-remontu-oborudovaniya/</t>
+    </r>
+  </si>
+  <si>
+    <t>слесарь, сборщик, механик, монтажник, машиностроение</t>
+  </si>
+  <si>
+    <t>Обязанности контролера качества (ОТК): инструкции и проверка продукции</t>
+  </si>
+  <si>
+    <t>Обязанности контролера качества (ОТК): проверка продукции и нормы</t>
+  </si>
+  <si>
+    <t>obyazannosti-kontrolera-kachestva</t>
+  </si>
+  <si>
+    <t>Должностные обязанности контролера качества. Выявление брака, проведение испытаний и оформление паспортов качества.</t>
+  </si>
+  <si>
+    <t>контролер качества обязанности</t>
+  </si>
+  <si>
+    <t>https://obuchenieprosto.ru/blog/dolzhnostnye-obyazannosti-kontrolera-kachestva/</t>
+  </si>
+  <si>
+    <t>Контролер качества, Обучение рабочим профессиям, Должностные обязанности</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/kontroler-distancionnoe-obuchenie/
+https://dpoprof.ru/perepodgotovka/distancionnaya-perepodgotovka-kontroler-detalej-i-priborov/
+https://dpoprof.ru/perepodgotovka/kontroler/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-kontroler-kuznechno-pressovyh-rabot/</t>
+    </r>
+  </si>
+  <si>
+    <t>контролер, ОТК, инспектор, лаборант, эксперт</t>
+  </si>
+  <si>
+    <t>Самые высокооплачиваемые профессии 2026 года: рейтинг и обзор</t>
+  </si>
+  <si>
+    <t>Самые высокооплачиваемые профессии 2026 года: рейтинг и зарплаты</t>
+  </si>
+  <si>
+    <t>vysokooplachivaemye-professii-2026</t>
+  </si>
+  <si>
+    <t>Топ высокооплачиваемых профессий 2026 года. Обзор рынка труда: где платят больше всего и какие навыки ценятся работодателями.</t>
+  </si>
+  <si>
+    <t>высокооплачиваемые профессии 2026</t>
+  </si>
+  <si>
+    <t>https://ncpo.ru/blog/zarplata-inzhenera-v-rossii-2025-realnaya-statistika-po-vsem-spetsialnostyam/</t>
+  </si>
+  <si>
+    <t>Редакция и общие темы</t>
+  </si>
+  <si>
+    <t>Артём Ильич Афанасьев, Алёна Дмитриевна Богомолова, Константин Аркадьевич Ветров</t>
+  </si>
+  <si>
+    <t>Высокооплачиваемые профессии, Профориентация, Профессии</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/svarshhik-argonodugovaja-svarka-tig/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-energoaudit-zdanij-i-sooruzhenij/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-upravlenie-i-hr/
+https://dpoprof.ru/perepodgotovka/ekonomika-i-upravlenie/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/montazhnik-vysotnye-raboty/</t>
+    </r>
+  </si>
+  <si>
+    <t>профессии, карьера, зарплата, рынок, работа</t>
+  </si>
+  <si>
+    <t>Востребованные профессии для мужчин в 2026 году: список и перспективы</t>
+  </si>
+  <si>
+    <t>Востребованные профессии для мужчин в 2026: список и перспективы</t>
+  </si>
+  <si>
+    <t>vostrebovannye-professii-dlya-muzhchin</t>
+  </si>
+  <si>
+    <t>Топ профессий для мужчин, востребованных в 2026 году. Рабочие специальности, инженерия и IT: где найти стабильную работу.</t>
+  </si>
+  <si>
+    <t>востребованные профессии для мужчин</t>
+  </si>
+  <si>
+    <t>https://ncpo.ru/blog/top-50-samykh-vysokooplachivaemykh-professiy-v-rossii/</t>
+  </si>
+  <si>
+    <t>Артём Ильич Афанасьев, Константин Аркадьевич Ветров, Алёна Дмитриевна Богомолова</t>
+  </si>
+  <si>
+    <t>Профессии для мужчин, Профориентация, Профессии</t>
   </si>
   <si>
     <r>
@@ -961,15 +1115,14 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-upravlenie-proektami/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-dorognoe-stroitelstvo/
 </t>
     </r>
     <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-teploenergetika/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-gilishnoe-stroitelstvo/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-dorognoe-stroitelstvo/
-https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-biznes-kouching/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-montazhnik/
+https://dpoprof.ru/obuchenie/zavedujushhij-proizvodstvom/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-bankovskomu-delu/
 </t>
     </r>
     <r>
@@ -977,35 +1130,29 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/obuchenie/inzhener/</t>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-energoaudit-zdanij-i-sooruzhenij/</t>
     </r>
   </si>
   <si>
-    <t>Методист дистанционного обучения; Педагог дополнительного образования; Преподаватель; Разработчик электронных курсов</t>
+    <t>профессии, мужчины, карьера, специальности, работа</t>
   </si>
   <si>
-    <t>ДОПОГ 2026: как получить допуск для перевозки опасных грузов</t>
+    <t>Перспективные профессии для женщин в 2026 году: карьера и доход</t>
   </si>
   <si>
-    <t>ДОПОГ 2026: порядок получения допуска и требования к водителям</t>
+    <t>perspektivnye-professii-dlya-zhenshchin</t>
   </si>
   <si>
-    <t>dopog-2026-poryadok-polucheniya-dopuska-i-trebovaniya-k-voditelyam</t>
+    <t>Список перспективных профессий для женщин. Тренды 2026 года, возможности для карьерного роста и высокооплачиваемые специальности.</t>
   </si>
   <si>
-    <t>Актуальные требования ДОПОГ 2026 года, порядок обучения, оформления допуска и работы с опасными грузами.</t>
+    <t>перспективные профессии для женщин</t>
   </si>
   <si>
-    <t>ДОПОГ 2026</t>
+    <t>https://ncpo.ru/blog/vostrebovannye-professii-dlya-muzhchin-2025-v-rossii-reyting-luchshikh/</t>
   </si>
   <si>
-    <t>https://centrfenix.ru/articles/dopog-2026-kak-oformit-dopusk-i-rabotat-s-opasnymi-gruzami/</t>
-  </si>
-  <si>
-    <t>Безопасность и охрана труда</t>
-  </si>
-  <si>
-    <t>Юрий Борисович Гончаров; Тимур Эдуардович Рахманов</t>
+    <t>Профессии для женщин, Профориентация, Профессии</t>
   </si>
   <si>
     <r>
@@ -1013,13 +1160,14 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/voditel-shtabelera-distancionnoe-obuchenie/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-upravlenie-i-hr/
 </t>
     </r>
     <r>
       <rPr/>
-      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-voditelya-pogruzchika/
-https://dpoprof.ru/perepodgotovka/voditel-pogruzchika/
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/uchitel-nachalnyh-klassov-distancionnoe-obuchenie/
+https://dpoprof.ru/obuchenie-medpersonala/instruktor-po-lfk-distancionnoe-obuchenie/
+https://dpoprof.ru/perepodgotovka/landshaftnaya-arhitektura/
 </t>
     </r>
     <r>
@@ -1027,18 +1175,229 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://dpoprof.ru/povyshenie/povyshenie-kvalifikaczii-voditelei/</t>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-budgetnomu-ushetu/</t>
     </r>
   </si>
   <si>
-    <t>Водитель ДОПОГ; Специалист по логистике; Водитель бензовоза; Специалист по транспортной безопасности</t>
+    <t>профессии, женщины, карьера, специальности, работа</t>
+  </si>
+  <si>
+    <t>Удаленная работа для мам в декрете 2025: вакансии и идеи</t>
+  </si>
+  <si>
+    <t>Удаленная работа для мам в 2025 году: вакансии и советы</t>
+  </si>
+  <si>
+    <t>udalennaya-rabota-dlya-mam</t>
+  </si>
+  <si>
+    <t>Кем работать маме в декрете из дома? Подборка профессий для удаленной работы в 2025 году с гибким графиком.</t>
+  </si>
+  <si>
+    <t>удаленная работа для мам 2025</t>
+  </si>
+  <si>
+    <t>https://ncpo.ru/blog/zhenskie-professii-budushchego-2025-samye-perspektivnye-napravleniya/</t>
+  </si>
+  <si>
+    <t>Удаленная работа, Профориентация, Профессии</t>
+  </si>
+  <si>
+    <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-korrektora/
+https://dpoprof.ru/obuchenie/repetitor-distancionnoe-obuchenie/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-upravlenie-i-hr/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-buhgalterskij-uchet-analiz-i-audit/
+https://dpoprof.ru/perepodgotovka/perepodgotovka-na-menedzhera-it-proektov/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-upravlenie-proektami/</t>
+  </si>
+  <si>
+    <t>фриланс, копирайтер, оператор, менеджер, маркетолог</t>
+  </si>
+  <si>
+    <t>Какие профессии исчезнут к 2030 году: прогноз рынка труда</t>
+  </si>
+  <si>
+    <t>Какие профессии исчезнут к 2030 году: прогноз и риски</t>
+  </si>
+  <si>
+    <t>kakie-professii-ischeznut-k-2030</t>
+  </si>
+  <si>
+    <t>Прогноз рынка труда: список профессий, которые могут исчезнуть к 2030 году из-за автоматизации. Кем не стоит становиться.</t>
+  </si>
+  <si>
+    <t>какие профессии исчезнут к 2030</t>
+  </si>
+  <si>
+    <t>https://ncpo.ru/blog/udalennye-professii-dlya-mam-2025-top-20-s-gibkim-grafikom/</t>
+  </si>
+  <si>
+    <t>Артём Ильич Афанасьев, Константин Аркадьевич Ветров, Тимур Эдуардович Рахманов</t>
+  </si>
+  <si>
+    <t>Профессии будущего, Профориентация, Профессии</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/logoped-distancionnoe-obuchenie/
+https://dpoprof.ru/obuchenie/jelektrogazosvarshhik/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve">https://dpoprof.ru/perepodgotovka/slesar-distancionnaja-perepodgotovka/
+</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>https://dpoprof.ru/obuchenie-medpersonala/vrach-pediatr-distancionnoe-obuchenie/
+https://dpoprof.ru/obuchenie/repetitor-distancionnoe-obuchenie/</t>
+    </r>
+  </si>
+  <si>
+    <t>автоматизация, роботизация, профессии, рынок, ИИ</t>
+  </si>
+  <si>
+    <t>Зарплата сварщика на вахте в 2026 году: ставки и условия труда</t>
+  </si>
+  <si>
+    <t>Зарплата сварщика на вахте в 2026 году: сколько реально платят</t>
+  </si>
+  <si>
+    <t>zarplata-svarshchika-na-vakhte</t>
+  </si>
+  <si>
+    <t>Обзор зарплат сварщиков вахтовым методом. Ставки, надбавки за север и условия проживания. На какую сумму можно рассчитывать?</t>
+  </si>
+  <si>
+    <t>зарплата сварщика на вахте</t>
+  </si>
+  <si>
+    <t>https://ncpo.ru/blog/ischezayushchie-professii-2025-kakie-spetsialnosti-skoro-ischeznut-i-chto-delat-rabotnikam/</t>
+  </si>
+  <si>
+    <t>Сварщик, Обучение рабочим профессиям, Зарплата по профессии</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-svarschik/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-elektrosvarshika/
+https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-elektrogazosvarshik-vrezchik/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-vyshkomontazhnik-svarshik/</t>
+    </r>
+  </si>
+  <si>
+    <t>сварщик, вахта, зарплата, Север, металлоконструкции</t>
+  </si>
+  <si>
+    <t>Охрана труда в школе в 2026 году: организация и документы</t>
+  </si>
+  <si>
+    <t>Охрана труда в школе 2026: новые требования и организация</t>
+  </si>
+  <si>
+    <t>okhrana-truda-v-shkole-2026</t>
+  </si>
+  <si>
+    <t>Как организовать охрану труда в школе в 2026 году. Список обязательных документов, инструктажи для учителей и ответственность директора.</t>
+  </si>
+  <si>
+    <t>охрана труда в школе 2026</t>
+  </si>
+  <si>
+    <t>https://ncpo.ru/blog/kak-organizovat-ohranu-truda-v-obrazovatelnom-uchrezhdenii-v-2025-godu/</t>
+  </si>
+  <si>
+    <t>Безопасность и охрана труда</t>
+  </si>
+  <si>
+    <t>Сергей Александрович Николаев, Тимур Эдуардович Рахманов, Артём Ильич Афанасьев</t>
+  </si>
+  <si>
+    <t>Охрана труда в школе, Обучение охране труда, Охрана труда</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-bibliotechnoe-delo/
+https://dpoprof.ru/obuchenie/uchitel-defektolog-distancionnoe-obuchenie/
+https://dpoprof.ru/obuchenie/uchitel-psihologii-distancionnoe-obuchenie/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://dpoprof.ru/obuchenie/upravlenie-v-sfere-obrazovanija-distancionnoe-obuchenie/</t>
+    </r>
+  </si>
+  <si>
+    <t>охрана, школа, инструктаж, безопасность, директор</t>
+  </si>
+  <si>
+    <t>Целевой инструктаж по охране труда 2026: порядок и правила проведения</t>
+  </si>
+  <si>
+    <t>Целевой инструктаж по охране труда 2026: когда и как проводить</t>
+  </si>
+  <si>
+    <t>tselevoy-instruktazh-po-okhrane-truda-2026</t>
+  </si>
+  <si>
+    <t>Правила проведения целевого инструктажа в 2026 году. В каких случаях он обязателен, как фиксировать в журнале и образец оформления.</t>
+  </si>
+  <si>
+    <t>целевой инструктаж 2026</t>
+  </si>
+  <si>
+    <t>https://ncpo.ru/blog/celevoj-instruktazh-po-ohrane-truda-v-2025-godu-kogda-i-komu-nuzhen-kto-provodit/</t>
+  </si>
+  <si>
+    <t>Целевой инструктаж, Обучение охране труда, Охрана труда</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-gazosvarshika/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve">https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-na-defektoskopista/
+</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>https://dpoprof.ru/obuchenie/distancionnoe-obuchenie-operator-tovarnyj/
+https://dpoprof.ru/obuchenie/svarshhik-argonodugovaja-svarka-tig/
+https://dpoprof.ru/perepodgotovka/elektrosvarshhik/</t>
+    </r>
+  </si>
+  <si>
+    <t>инструктаж, охрана, безопасность, журнал, допуск</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="12">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1057,15 +1416,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <u/>
       <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1076,6 +1467,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF38761D"/>
         <bgColor rgb="FF38761D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD1DC"/>
+        <bgColor rgb="FFEAD1DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1099,7 +1502,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1112,19 +1515,73 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1344,17 +1801,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.88"/>
+    <col customWidth="1" min="1" max="1" width="3.0"/>
     <col customWidth="1" min="2" max="2" width="25.0"/>
     <col customWidth="1" min="3" max="3" width="21.88"/>
     <col customWidth="1" min="4" max="4" width="16.0"/>
-    <col customWidth="1" min="5" max="5" width="30.88"/>
+    <col customWidth="1" min="5" max="5" width="24.25"/>
     <col customWidth="1" min="6" max="6" width="17.13"/>
-    <col customWidth="1" min="7" max="7" width="24.25"/>
+    <col customWidth="1" min="7" max="7" width="19.13"/>
     <col customWidth="1" min="8" max="8" width="14.38"/>
     <col customWidth="1" min="9" max="9" width="18.13"/>
-    <col customWidth="1" min="10" max="10" width="16.25"/>
-    <col customWidth="1" min="11" max="11" width="16.75"/>
+    <col customWidth="1" min="11" max="11" width="16.25"/>
+    <col customWidth="1" min="12" max="12" width="44.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1391,7 +1848,9 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3"/>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
@@ -1414,259 +1873,269 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4">
-        <v>37.0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="4" t="s">
+        <v>9.0</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="H2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
+      <c r="K2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4">
-        <v>38.0</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="4" t="s">
+        <v>10.0</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="H3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
+      <c r="I3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4">
-        <v>39.0</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="4" t="s">
+        <v>11.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4">
-        <v>40.0</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="4" t="s">
+        <v>12.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="10"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="12">
+        <v>13.0</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="4">
-        <v>41.0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="3"/>
+      <c r="I6" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -1688,480 +2157,498 @@
       <c r="AE6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4">
-        <v>42.0</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
+      <c r="A7" s="18">
+        <v>14.0</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="4">
-        <v>43.0</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8" s="6" t="s">
+      <c r="A8" s="18">
+        <v>15.0</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
+      <c r="I8" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="4">
-        <v>44.0</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
+      <c r="A9" s="18">
+        <v>16.0</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="4">
-        <v>45.0</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
+      <c r="A10" s="18">
+        <v>17.0</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4">
-        <v>46.0</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
+      <c r="A11" s="18">
+        <v>18.0</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="24"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+      <c r="X11" s="24"/>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="24"/>
+      <c r="AA11" s="24"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="24"/>
+      <c r="AD11" s="24"/>
+      <c r="AE11" s="24"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="4">
-        <v>47.0</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="A12" s="18">
+        <v>19.0</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
+      <c r="I12" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
+      <c r="AE12" s="24"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4">
-        <v>48.0</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
+      <c r="A13" s="18">
+        <v>20.0</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="24"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="24"/>
+      <c r="X13" s="24"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="24"/>
+      <c r="AD13" s="24"/>
+      <c r="AE13" s="24"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="4">
-        <v>49.0</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
+      <c r="A14" s="18">
+        <v>21.0</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="4">
-        <v>50.0</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="A15" s="12">
+        <v>22.0</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="H15" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L15" s="3"/>
+      <c r="J15" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>151</v>
+      </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -2183,40 +2670,42 @@
       <c r="AE15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="4">
-        <v>51.0</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="L16" s="3"/>
+      <c r="A16" s="12">
+        <v>23.0</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -2238,40 +2727,42 @@
       <c r="AE16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="4">
-        <v>52.0</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="L17" s="3"/>
+      <c r="A17" s="12">
+        <v>24.0</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>172</v>
+      </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -2293,40 +2784,42 @@
       <c r="AE17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="4">
-        <v>53.0</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="L18" s="3"/>
+      <c r="A18" s="12">
+        <v>25.0</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>182</v>
+      </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -2348,40 +2841,42 @@
       <c r="AE18" s="3"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="4">
-        <v>54.0</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="L19" s="3"/>
+      <c r="A19" s="12">
+        <v>26.0</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>193</v>
+      </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -2403,40 +2898,42 @@
       <c r="AE19" s="3"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="4">
-        <v>55.0</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="L20" s="3"/>
+      <c r="A20" s="12">
+        <v>27.0</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>203</v>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -2458,40 +2955,42 @@
       <c r="AE20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4">
-        <v>56.0</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="L21" s="3"/>
+      <c r="A21" s="12">
+        <v>28.0</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>213</v>
+      </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -2513,40 +3012,42 @@
       <c r="AE21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4">
-        <v>57.0</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="L22" s="3"/>
+      <c r="A22" s="12">
+        <v>29.0</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>222</v>
+      </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
@@ -2568,40 +3069,42 @@
       <c r="AE22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4">
-        <v>58.0</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="L23" s="3"/>
+      <c r="A23" s="12">
+        <v>30.0</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>233</v>
+      </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -2623,40 +3126,42 @@
       <c r="AE23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4">
-        <v>59.0</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="L24" s="3"/>
+      <c r="A24" s="12">
+        <v>31.0</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>243</v>
+      </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -2678,40 +3183,42 @@
       <c r="AE24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4">
-        <v>60.0</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="L25" s="3"/>
+      <c r="A25" s="12">
+        <v>32.0</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>251</v>
+      </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -2733,18 +3240,42 @@
       <c r="AE25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+      <c r="A26" s="12">
+        <v>33.0</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="K26" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>260</v>
+      </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -2766,18 +3297,42 @@
       <c r="AE26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
+      <c r="A27" s="12">
+        <v>34.0</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>270</v>
+      </c>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -2799,18 +3354,42 @@
       <c r="AE27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
+      <c r="A28" s="12">
+        <v>35.0</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>279</v>
+      </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -2832,18 +3411,42 @@
       <c r="AE28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
+      <c r="A29" s="12">
+        <v>36.0</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>290</v>
+      </c>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -2865,18 +3468,42 @@
       <c r="AE29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
+      <c r="A30" s="12">
+        <v>37.0</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>299</v>
+      </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -32531,1242 +33158,67 @@
       <c r="AD928" s="3"/>
       <c r="AE928" s="3"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="3"/>
-      <c r="B929" s="3"/>
-      <c r="C929" s="3"/>
-      <c r="D929" s="3"/>
-      <c r="E929" s="3"/>
-      <c r="F929" s="3"/>
-      <c r="G929" s="3"/>
-      <c r="H929" s="3"/>
-      <c r="I929" s="3"/>
-      <c r="J929" s="3"/>
-      <c r="K929" s="3"/>
-      <c r="L929" s="3"/>
-      <c r="M929" s="3"/>
-      <c r="N929" s="3"/>
-      <c r="O929" s="3"/>
-      <c r="P929" s="3"/>
-      <c r="Q929" s="3"/>
-      <c r="R929" s="3"/>
-      <c r="S929" s="3"/>
-      <c r="T929" s="3"/>
-      <c r="U929" s="3"/>
-      <c r="V929" s="3"/>
-      <c r="W929" s="3"/>
-      <c r="X929" s="3"/>
-      <c r="Y929" s="3"/>
-      <c r="Z929" s="3"/>
-      <c r="AA929" s="3"/>
-      <c r="AB929" s="3"/>
-      <c r="AC929" s="3"/>
-      <c r="AD929" s="3"/>
-      <c r="AE929" s="3"/>
-    </row>
-    <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="3"/>
-      <c r="B930" s="3"/>
-      <c r="C930" s="3"/>
-      <c r="D930" s="3"/>
-      <c r="E930" s="3"/>
-      <c r="F930" s="3"/>
-      <c r="G930" s="3"/>
-      <c r="H930" s="3"/>
-      <c r="I930" s="3"/>
-      <c r="J930" s="3"/>
-      <c r="K930" s="3"/>
-      <c r="L930" s="3"/>
-      <c r="M930" s="3"/>
-      <c r="N930" s="3"/>
-      <c r="O930" s="3"/>
-      <c r="P930" s="3"/>
-      <c r="Q930" s="3"/>
-      <c r="R930" s="3"/>
-      <c r="S930" s="3"/>
-      <c r="T930" s="3"/>
-      <c r="U930" s="3"/>
-      <c r="V930" s="3"/>
-      <c r="W930" s="3"/>
-      <c r="X930" s="3"/>
-      <c r="Y930" s="3"/>
-      <c r="Z930" s="3"/>
-      <c r="AA930" s="3"/>
-      <c r="AB930" s="3"/>
-      <c r="AC930" s="3"/>
-      <c r="AD930" s="3"/>
-      <c r="AE930" s="3"/>
-    </row>
-    <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="3"/>
-      <c r="B931" s="3"/>
-      <c r="C931" s="3"/>
-      <c r="D931" s="3"/>
-      <c r="E931" s="3"/>
-      <c r="F931" s="3"/>
-      <c r="G931" s="3"/>
-      <c r="H931" s="3"/>
-      <c r="I931" s="3"/>
-      <c r="J931" s="3"/>
-      <c r="K931" s="3"/>
-      <c r="L931" s="3"/>
-      <c r="M931" s="3"/>
-      <c r="N931" s="3"/>
-      <c r="O931" s="3"/>
-      <c r="P931" s="3"/>
-      <c r="Q931" s="3"/>
-      <c r="R931" s="3"/>
-      <c r="S931" s="3"/>
-      <c r="T931" s="3"/>
-      <c r="U931" s="3"/>
-      <c r="V931" s="3"/>
-      <c r="W931" s="3"/>
-      <c r="X931" s="3"/>
-      <c r="Y931" s="3"/>
-      <c r="Z931" s="3"/>
-      <c r="AA931" s="3"/>
-      <c r="AB931" s="3"/>
-      <c r="AC931" s="3"/>
-      <c r="AD931" s="3"/>
-      <c r="AE931" s="3"/>
-    </row>
-    <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="3"/>
-      <c r="B932" s="3"/>
-      <c r="C932" s="3"/>
-      <c r="D932" s="3"/>
-      <c r="E932" s="3"/>
-      <c r="F932" s="3"/>
-      <c r="G932" s="3"/>
-      <c r="H932" s="3"/>
-      <c r="I932" s="3"/>
-      <c r="J932" s="3"/>
-      <c r="K932" s="3"/>
-      <c r="L932" s="3"/>
-      <c r="M932" s="3"/>
-      <c r="N932" s="3"/>
-      <c r="O932" s="3"/>
-      <c r="P932" s="3"/>
-      <c r="Q932" s="3"/>
-      <c r="R932" s="3"/>
-      <c r="S932" s="3"/>
-      <c r="T932" s="3"/>
-      <c r="U932" s="3"/>
-      <c r="V932" s="3"/>
-      <c r="W932" s="3"/>
-      <c r="X932" s="3"/>
-      <c r="Y932" s="3"/>
-      <c r="Z932" s="3"/>
-      <c r="AA932" s="3"/>
-      <c r="AB932" s="3"/>
-      <c r="AC932" s="3"/>
-      <c r="AD932" s="3"/>
-      <c r="AE932" s="3"/>
-    </row>
-    <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="3"/>
-      <c r="B933" s="3"/>
-      <c r="C933" s="3"/>
-      <c r="D933" s="3"/>
-      <c r="E933" s="3"/>
-      <c r="F933" s="3"/>
-      <c r="G933" s="3"/>
-      <c r="H933" s="3"/>
-      <c r="I933" s="3"/>
-      <c r="J933" s="3"/>
-      <c r="K933" s="3"/>
-      <c r="L933" s="3"/>
-      <c r="M933" s="3"/>
-      <c r="N933" s="3"/>
-      <c r="O933" s="3"/>
-      <c r="P933" s="3"/>
-      <c r="Q933" s="3"/>
-      <c r="R933" s="3"/>
-      <c r="S933" s="3"/>
-      <c r="T933" s="3"/>
-      <c r="U933" s="3"/>
-      <c r="V933" s="3"/>
-      <c r="W933" s="3"/>
-      <c r="X933" s="3"/>
-      <c r="Y933" s="3"/>
-      <c r="Z933" s="3"/>
-      <c r="AA933" s="3"/>
-      <c r="AB933" s="3"/>
-      <c r="AC933" s="3"/>
-      <c r="AD933" s="3"/>
-      <c r="AE933" s="3"/>
-    </row>
-    <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="3"/>
-      <c r="B934" s="3"/>
-      <c r="C934" s="3"/>
-      <c r="D934" s="3"/>
-      <c r="E934" s="3"/>
-      <c r="F934" s="3"/>
-      <c r="G934" s="3"/>
-      <c r="H934" s="3"/>
-      <c r="I934" s="3"/>
-      <c r="J934" s="3"/>
-      <c r="K934" s="3"/>
-      <c r="L934" s="3"/>
-      <c r="M934" s="3"/>
-      <c r="N934" s="3"/>
-      <c r="O934" s="3"/>
-      <c r="P934" s="3"/>
-      <c r="Q934" s="3"/>
-      <c r="R934" s="3"/>
-      <c r="S934" s="3"/>
-      <c r="T934" s="3"/>
-      <c r="U934" s="3"/>
-      <c r="V934" s="3"/>
-      <c r="W934" s="3"/>
-      <c r="X934" s="3"/>
-      <c r="Y934" s="3"/>
-      <c r="Z934" s="3"/>
-      <c r="AA934" s="3"/>
-      <c r="AB934" s="3"/>
-      <c r="AC934" s="3"/>
-      <c r="AD934" s="3"/>
-      <c r="AE934" s="3"/>
-    </row>
-    <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="3"/>
-      <c r="B935" s="3"/>
-      <c r="C935" s="3"/>
-      <c r="D935" s="3"/>
-      <c r="E935" s="3"/>
-      <c r="F935" s="3"/>
-      <c r="G935" s="3"/>
-      <c r="H935" s="3"/>
-      <c r="I935" s="3"/>
-      <c r="J935" s="3"/>
-      <c r="K935" s="3"/>
-      <c r="L935" s="3"/>
-      <c r="M935" s="3"/>
-      <c r="N935" s="3"/>
-      <c r="O935" s="3"/>
-      <c r="P935" s="3"/>
-      <c r="Q935" s="3"/>
-      <c r="R935" s="3"/>
-      <c r="S935" s="3"/>
-      <c r="T935" s="3"/>
-      <c r="U935" s="3"/>
-      <c r="V935" s="3"/>
-      <c r="W935" s="3"/>
-      <c r="X935" s="3"/>
-      <c r="Y935" s="3"/>
-      <c r="Z935" s="3"/>
-      <c r="AA935" s="3"/>
-      <c r="AB935" s="3"/>
-      <c r="AC935" s="3"/>
-      <c r="AD935" s="3"/>
-      <c r="AE935" s="3"/>
-    </row>
-    <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="3"/>
-      <c r="B936" s="3"/>
-      <c r="C936" s="3"/>
-      <c r="D936" s="3"/>
-      <c r="E936" s="3"/>
-      <c r="F936" s="3"/>
-      <c r="G936" s="3"/>
-      <c r="H936" s="3"/>
-      <c r="I936" s="3"/>
-      <c r="J936" s="3"/>
-      <c r="K936" s="3"/>
-      <c r="L936" s="3"/>
-      <c r="M936" s="3"/>
-      <c r="N936" s="3"/>
-      <c r="O936" s="3"/>
-      <c r="P936" s="3"/>
-      <c r="Q936" s="3"/>
-      <c r="R936" s="3"/>
-      <c r="S936" s="3"/>
-      <c r="T936" s="3"/>
-      <c r="U936" s="3"/>
-      <c r="V936" s="3"/>
-      <c r="W936" s="3"/>
-      <c r="X936" s="3"/>
-      <c r="Y936" s="3"/>
-      <c r="Z936" s="3"/>
-      <c r="AA936" s="3"/>
-      <c r="AB936" s="3"/>
-      <c r="AC936" s="3"/>
-      <c r="AD936" s="3"/>
-      <c r="AE936" s="3"/>
-    </row>
-    <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="3"/>
-      <c r="B937" s="3"/>
-      <c r="C937" s="3"/>
-      <c r="D937" s="3"/>
-      <c r="E937" s="3"/>
-      <c r="F937" s="3"/>
-      <c r="G937" s="3"/>
-      <c r="H937" s="3"/>
-      <c r="I937" s="3"/>
-      <c r="J937" s="3"/>
-      <c r="K937" s="3"/>
-      <c r="L937" s="3"/>
-      <c r="M937" s="3"/>
-      <c r="N937" s="3"/>
-      <c r="O937" s="3"/>
-      <c r="P937" s="3"/>
-      <c r="Q937" s="3"/>
-      <c r="R937" s="3"/>
-      <c r="S937" s="3"/>
-      <c r="T937" s="3"/>
-      <c r="U937" s="3"/>
-      <c r="V937" s="3"/>
-      <c r="W937" s="3"/>
-      <c r="X937" s="3"/>
-      <c r="Y937" s="3"/>
-      <c r="Z937" s="3"/>
-      <c r="AA937" s="3"/>
-      <c r="AB937" s="3"/>
-      <c r="AC937" s="3"/>
-      <c r="AD937" s="3"/>
-      <c r="AE937" s="3"/>
-    </row>
-    <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="3"/>
-      <c r="B938" s="3"/>
-      <c r="C938" s="3"/>
-      <c r="D938" s="3"/>
-      <c r="E938" s="3"/>
-      <c r="F938" s="3"/>
-      <c r="G938" s="3"/>
-      <c r="H938" s="3"/>
-      <c r="I938" s="3"/>
-      <c r="J938" s="3"/>
-      <c r="K938" s="3"/>
-      <c r="L938" s="3"/>
-      <c r="M938" s="3"/>
-      <c r="N938" s="3"/>
-      <c r="O938" s="3"/>
-      <c r="P938" s="3"/>
-      <c r="Q938" s="3"/>
-      <c r="R938" s="3"/>
-      <c r="S938" s="3"/>
-      <c r="T938" s="3"/>
-      <c r="U938" s="3"/>
-      <c r="V938" s="3"/>
-      <c r="W938" s="3"/>
-      <c r="X938" s="3"/>
-      <c r="Y938" s="3"/>
-      <c r="Z938" s="3"/>
-      <c r="AA938" s="3"/>
-      <c r="AB938" s="3"/>
-      <c r="AC938" s="3"/>
-      <c r="AD938" s="3"/>
-      <c r="AE938" s="3"/>
-    </row>
-    <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="3"/>
-      <c r="B939" s="3"/>
-      <c r="C939" s="3"/>
-      <c r="D939" s="3"/>
-      <c r="E939" s="3"/>
-      <c r="F939" s="3"/>
-      <c r="G939" s="3"/>
-      <c r="H939" s="3"/>
-      <c r="I939" s="3"/>
-      <c r="J939" s="3"/>
-      <c r="K939" s="3"/>
-      <c r="L939" s="3"/>
-      <c r="M939" s="3"/>
-      <c r="N939" s="3"/>
-      <c r="O939" s="3"/>
-      <c r="P939" s="3"/>
-      <c r="Q939" s="3"/>
-      <c r="R939" s="3"/>
-      <c r="S939" s="3"/>
-      <c r="T939" s="3"/>
-      <c r="U939" s="3"/>
-      <c r="V939" s="3"/>
-      <c r="W939" s="3"/>
-      <c r="X939" s="3"/>
-      <c r="Y939" s="3"/>
-      <c r="Z939" s="3"/>
-      <c r="AA939" s="3"/>
-      <c r="AB939" s="3"/>
-      <c r="AC939" s="3"/>
-      <c r="AD939" s="3"/>
-      <c r="AE939" s="3"/>
-    </row>
-    <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="3"/>
-      <c r="B940" s="3"/>
-      <c r="C940" s="3"/>
-      <c r="D940" s="3"/>
-      <c r="E940" s="3"/>
-      <c r="F940" s="3"/>
-      <c r="G940" s="3"/>
-      <c r="H940" s="3"/>
-      <c r="I940" s="3"/>
-      <c r="J940" s="3"/>
-      <c r="K940" s="3"/>
-      <c r="L940" s="3"/>
-      <c r="M940" s="3"/>
-      <c r="N940" s="3"/>
-      <c r="O940" s="3"/>
-      <c r="P940" s="3"/>
-      <c r="Q940" s="3"/>
-      <c r="R940" s="3"/>
-      <c r="S940" s="3"/>
-      <c r="T940" s="3"/>
-      <c r="U940" s="3"/>
-      <c r="V940" s="3"/>
-      <c r="W940" s="3"/>
-      <c r="X940" s="3"/>
-      <c r="Y940" s="3"/>
-      <c r="Z940" s="3"/>
-      <c r="AA940" s="3"/>
-      <c r="AB940" s="3"/>
-      <c r="AC940" s="3"/>
-      <c r="AD940" s="3"/>
-      <c r="AE940" s="3"/>
-    </row>
-    <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="3"/>
-      <c r="B941" s="3"/>
-      <c r="C941" s="3"/>
-      <c r="D941" s="3"/>
-      <c r="E941" s="3"/>
-      <c r="F941" s="3"/>
-      <c r="G941" s="3"/>
-      <c r="H941" s="3"/>
-      <c r="I941" s="3"/>
-      <c r="J941" s="3"/>
-      <c r="K941" s="3"/>
-      <c r="L941" s="3"/>
-      <c r="M941" s="3"/>
-      <c r="N941" s="3"/>
-      <c r="O941" s="3"/>
-      <c r="P941" s="3"/>
-      <c r="Q941" s="3"/>
-      <c r="R941" s="3"/>
-      <c r="S941" s="3"/>
-      <c r="T941" s="3"/>
-      <c r="U941" s="3"/>
-      <c r="V941" s="3"/>
-      <c r="W941" s="3"/>
-      <c r="X941" s="3"/>
-      <c r="Y941" s="3"/>
-      <c r="Z941" s="3"/>
-      <c r="AA941" s="3"/>
-      <c r="AB941" s="3"/>
-      <c r="AC941" s="3"/>
-      <c r="AD941" s="3"/>
-      <c r="AE941" s="3"/>
-    </row>
-    <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="3"/>
-      <c r="B942" s="3"/>
-      <c r="C942" s="3"/>
-      <c r="D942" s="3"/>
-      <c r="E942" s="3"/>
-      <c r="F942" s="3"/>
-      <c r="G942" s="3"/>
-      <c r="H942" s="3"/>
-      <c r="I942" s="3"/>
-      <c r="J942" s="3"/>
-      <c r="K942" s="3"/>
-      <c r="L942" s="3"/>
-      <c r="M942" s="3"/>
-      <c r="N942" s="3"/>
-      <c r="O942" s="3"/>
-      <c r="P942" s="3"/>
-      <c r="Q942" s="3"/>
-      <c r="R942" s="3"/>
-      <c r="S942" s="3"/>
-      <c r="T942" s="3"/>
-      <c r="U942" s="3"/>
-      <c r="V942" s="3"/>
-      <c r="W942" s="3"/>
-      <c r="X942" s="3"/>
-      <c r="Y942" s="3"/>
-      <c r="Z942" s="3"/>
-      <c r="AA942" s="3"/>
-      <c r="AB942" s="3"/>
-      <c r="AC942" s="3"/>
-      <c r="AD942" s="3"/>
-      <c r="AE942" s="3"/>
-    </row>
-    <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="3"/>
-      <c r="B943" s="3"/>
-      <c r="C943" s="3"/>
-      <c r="D943" s="3"/>
-      <c r="E943" s="3"/>
-      <c r="F943" s="3"/>
-      <c r="G943" s="3"/>
-      <c r="H943" s="3"/>
-      <c r="I943" s="3"/>
-      <c r="J943" s="3"/>
-      <c r="K943" s="3"/>
-      <c r="L943" s="3"/>
-      <c r="M943" s="3"/>
-      <c r="N943" s="3"/>
-      <c r="O943" s="3"/>
-      <c r="P943" s="3"/>
-      <c r="Q943" s="3"/>
-      <c r="R943" s="3"/>
-      <c r="S943" s="3"/>
-      <c r="T943" s="3"/>
-      <c r="U943" s="3"/>
-      <c r="V943" s="3"/>
-      <c r="W943" s="3"/>
-      <c r="X943" s="3"/>
-      <c r="Y943" s="3"/>
-      <c r="Z943" s="3"/>
-      <c r="AA943" s="3"/>
-      <c r="AB943" s="3"/>
-      <c r="AC943" s="3"/>
-      <c r="AD943" s="3"/>
-      <c r="AE943" s="3"/>
-    </row>
-    <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="3"/>
-      <c r="B944" s="3"/>
-      <c r="C944" s="3"/>
-      <c r="D944" s="3"/>
-      <c r="E944" s="3"/>
-      <c r="F944" s="3"/>
-      <c r="G944" s="3"/>
-      <c r="H944" s="3"/>
-      <c r="I944" s="3"/>
-      <c r="J944" s="3"/>
-      <c r="K944" s="3"/>
-      <c r="L944" s="3"/>
-      <c r="M944" s="3"/>
-      <c r="N944" s="3"/>
-      <c r="O944" s="3"/>
-      <c r="P944" s="3"/>
-      <c r="Q944" s="3"/>
-      <c r="R944" s="3"/>
-      <c r="S944" s="3"/>
-      <c r="T944" s="3"/>
-      <c r="U944" s="3"/>
-      <c r="V944" s="3"/>
-      <c r="W944" s="3"/>
-      <c r="X944" s="3"/>
-      <c r="Y944" s="3"/>
-      <c r="Z944" s="3"/>
-      <c r="AA944" s="3"/>
-      <c r="AB944" s="3"/>
-      <c r="AC944" s="3"/>
-      <c r="AD944" s="3"/>
-      <c r="AE944" s="3"/>
-    </row>
-    <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="3"/>
-      <c r="B945" s="3"/>
-      <c r="C945" s="3"/>
-      <c r="D945" s="3"/>
-      <c r="E945" s="3"/>
-      <c r="F945" s="3"/>
-      <c r="G945" s="3"/>
-      <c r="H945" s="3"/>
-      <c r="I945" s="3"/>
-      <c r="J945" s="3"/>
-      <c r="K945" s="3"/>
-      <c r="L945" s="3"/>
-      <c r="M945" s="3"/>
-      <c r="N945" s="3"/>
-      <c r="O945" s="3"/>
-      <c r="P945" s="3"/>
-      <c r="Q945" s="3"/>
-      <c r="R945" s="3"/>
-      <c r="S945" s="3"/>
-      <c r="T945" s="3"/>
-      <c r="U945" s="3"/>
-      <c r="V945" s="3"/>
-      <c r="W945" s="3"/>
-      <c r="X945" s="3"/>
-      <c r="Y945" s="3"/>
-      <c r="Z945" s="3"/>
-      <c r="AA945" s="3"/>
-      <c r="AB945" s="3"/>
-      <c r="AC945" s="3"/>
-      <c r="AD945" s="3"/>
-      <c r="AE945" s="3"/>
-    </row>
-    <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="3"/>
-      <c r="B946" s="3"/>
-      <c r="C946" s="3"/>
-      <c r="D946" s="3"/>
-      <c r="E946" s="3"/>
-      <c r="F946" s="3"/>
-      <c r="G946" s="3"/>
-      <c r="H946" s="3"/>
-      <c r="I946" s="3"/>
-      <c r="J946" s="3"/>
-      <c r="K946" s="3"/>
-      <c r="L946" s="3"/>
-      <c r="M946" s="3"/>
-      <c r="N946" s="3"/>
-      <c r="O946" s="3"/>
-      <c r="P946" s="3"/>
-      <c r="Q946" s="3"/>
-      <c r="R946" s="3"/>
-      <c r="S946" s="3"/>
-      <c r="T946" s="3"/>
-      <c r="U946" s="3"/>
-      <c r="V946" s="3"/>
-      <c r="W946" s="3"/>
-      <c r="X946" s="3"/>
-      <c r="Y946" s="3"/>
-      <c r="Z946" s="3"/>
-      <c r="AA946" s="3"/>
-      <c r="AB946" s="3"/>
-      <c r="AC946" s="3"/>
-      <c r="AD946" s="3"/>
-      <c r="AE946" s="3"/>
-    </row>
-    <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="3"/>
-      <c r="B947" s="3"/>
-      <c r="C947" s="3"/>
-      <c r="D947" s="3"/>
-      <c r="E947" s="3"/>
-      <c r="F947" s="3"/>
-      <c r="G947" s="3"/>
-      <c r="H947" s="3"/>
-      <c r="I947" s="3"/>
-      <c r="J947" s="3"/>
-      <c r="K947" s="3"/>
-      <c r="L947" s="3"/>
-      <c r="M947" s="3"/>
-      <c r="N947" s="3"/>
-      <c r="O947" s="3"/>
-      <c r="P947" s="3"/>
-      <c r="Q947" s="3"/>
-      <c r="R947" s="3"/>
-      <c r="S947" s="3"/>
-      <c r="T947" s="3"/>
-      <c r="U947" s="3"/>
-      <c r="V947" s="3"/>
-      <c r="W947" s="3"/>
-      <c r="X947" s="3"/>
-      <c r="Y947" s="3"/>
-      <c r="Z947" s="3"/>
-      <c r="AA947" s="3"/>
-      <c r="AB947" s="3"/>
-      <c r="AC947" s="3"/>
-      <c r="AD947" s="3"/>
-      <c r="AE947" s="3"/>
-    </row>
-    <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="3"/>
-      <c r="B948" s="3"/>
-      <c r="C948" s="3"/>
-      <c r="D948" s="3"/>
-      <c r="E948" s="3"/>
-      <c r="F948" s="3"/>
-      <c r="G948" s="3"/>
-      <c r="H948" s="3"/>
-      <c r="I948" s="3"/>
-      <c r="J948" s="3"/>
-      <c r="K948" s="3"/>
-      <c r="L948" s="3"/>
-      <c r="M948" s="3"/>
-      <c r="N948" s="3"/>
-      <c r="O948" s="3"/>
-      <c r="P948" s="3"/>
-      <c r="Q948" s="3"/>
-      <c r="R948" s="3"/>
-      <c r="S948" s="3"/>
-      <c r="T948" s="3"/>
-      <c r="U948" s="3"/>
-      <c r="V948" s="3"/>
-      <c r="W948" s="3"/>
-      <c r="X948" s="3"/>
-      <c r="Y948" s="3"/>
-      <c r="Z948" s="3"/>
-      <c r="AA948" s="3"/>
-      <c r="AB948" s="3"/>
-      <c r="AC948" s="3"/>
-      <c r="AD948" s="3"/>
-      <c r="AE948" s="3"/>
-    </row>
-    <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="3"/>
-      <c r="B949" s="3"/>
-      <c r="C949" s="3"/>
-      <c r="D949" s="3"/>
-      <c r="E949" s="3"/>
-      <c r="F949" s="3"/>
-      <c r="G949" s="3"/>
-      <c r="H949" s="3"/>
-      <c r="I949" s="3"/>
-      <c r="J949" s="3"/>
-      <c r="K949" s="3"/>
-      <c r="L949" s="3"/>
-      <c r="M949" s="3"/>
-      <c r="N949" s="3"/>
-      <c r="O949" s="3"/>
-      <c r="P949" s="3"/>
-      <c r="Q949" s="3"/>
-      <c r="R949" s="3"/>
-      <c r="S949" s="3"/>
-      <c r="T949" s="3"/>
-      <c r="U949" s="3"/>
-      <c r="V949" s="3"/>
-      <c r="W949" s="3"/>
-      <c r="X949" s="3"/>
-      <c r="Y949" s="3"/>
-      <c r="Z949" s="3"/>
-      <c r="AA949" s="3"/>
-      <c r="AB949" s="3"/>
-      <c r="AC949" s="3"/>
-      <c r="AD949" s="3"/>
-      <c r="AE949" s="3"/>
-    </row>
-    <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="3"/>
-      <c r="B950" s="3"/>
-      <c r="C950" s="3"/>
-      <c r="D950" s="3"/>
-      <c r="E950" s="3"/>
-      <c r="F950" s="3"/>
-      <c r="G950" s="3"/>
-      <c r="H950" s="3"/>
-      <c r="I950" s="3"/>
-      <c r="J950" s="3"/>
-      <c r="K950" s="3"/>
-      <c r="L950" s="3"/>
-      <c r="M950" s="3"/>
-      <c r="N950" s="3"/>
-      <c r="O950" s="3"/>
-      <c r="P950" s="3"/>
-      <c r="Q950" s="3"/>
-      <c r="R950" s="3"/>
-      <c r="S950" s="3"/>
-      <c r="T950" s="3"/>
-      <c r="U950" s="3"/>
-      <c r="V950" s="3"/>
-      <c r="W950" s="3"/>
-      <c r="X950" s="3"/>
-      <c r="Y950" s="3"/>
-      <c r="Z950" s="3"/>
-      <c r="AA950" s="3"/>
-      <c r="AB950" s="3"/>
-      <c r="AC950" s="3"/>
-      <c r="AD950" s="3"/>
-      <c r="AE950" s="3"/>
-    </row>
-    <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="3"/>
-      <c r="B951" s="3"/>
-      <c r="C951" s="3"/>
-      <c r="D951" s="3"/>
-      <c r="E951" s="3"/>
-      <c r="F951" s="3"/>
-      <c r="G951" s="3"/>
-      <c r="H951" s="3"/>
-      <c r="I951" s="3"/>
-      <c r="J951" s="3"/>
-      <c r="K951" s="3"/>
-      <c r="L951" s="3"/>
-      <c r="M951" s="3"/>
-      <c r="N951" s="3"/>
-      <c r="O951" s="3"/>
-      <c r="P951" s="3"/>
-      <c r="Q951" s="3"/>
-      <c r="R951" s="3"/>
-      <c r="S951" s="3"/>
-      <c r="T951" s="3"/>
-      <c r="U951" s="3"/>
-      <c r="V951" s="3"/>
-      <c r="W951" s="3"/>
-      <c r="X951" s="3"/>
-      <c r="Y951" s="3"/>
-      <c r="Z951" s="3"/>
-      <c r="AA951" s="3"/>
-      <c r="AB951" s="3"/>
-      <c r="AC951" s="3"/>
-      <c r="AD951" s="3"/>
-      <c r="AE951" s="3"/>
-    </row>
-    <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="3"/>
-      <c r="B952" s="3"/>
-      <c r="C952" s="3"/>
-      <c r="D952" s="3"/>
-      <c r="E952" s="3"/>
-      <c r="F952" s="3"/>
-      <c r="G952" s="3"/>
-      <c r="H952" s="3"/>
-      <c r="I952" s="3"/>
-      <c r="J952" s="3"/>
-      <c r="K952" s="3"/>
-      <c r="L952" s="3"/>
-      <c r="M952" s="3"/>
-      <c r="N952" s="3"/>
-      <c r="O952" s="3"/>
-      <c r="P952" s="3"/>
-      <c r="Q952" s="3"/>
-      <c r="R952" s="3"/>
-      <c r="S952" s="3"/>
-      <c r="T952" s="3"/>
-      <c r="U952" s="3"/>
-      <c r="V952" s="3"/>
-      <c r="W952" s="3"/>
-      <c r="X952" s="3"/>
-      <c r="Y952" s="3"/>
-      <c r="Z952" s="3"/>
-      <c r="AA952" s="3"/>
-      <c r="AB952" s="3"/>
-      <c r="AC952" s="3"/>
-      <c r="AD952" s="3"/>
-      <c r="AE952" s="3"/>
-    </row>
-    <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="3"/>
-      <c r="B953" s="3"/>
-      <c r="C953" s="3"/>
-      <c r="D953" s="3"/>
-      <c r="E953" s="3"/>
-      <c r="F953" s="3"/>
-      <c r="G953" s="3"/>
-      <c r="H953" s="3"/>
-      <c r="I953" s="3"/>
-      <c r="J953" s="3"/>
-      <c r="K953" s="3"/>
-      <c r="L953" s="3"/>
-      <c r="M953" s="3"/>
-      <c r="N953" s="3"/>
-      <c r="O953" s="3"/>
-      <c r="P953" s="3"/>
-      <c r="Q953" s="3"/>
-      <c r="R953" s="3"/>
-      <c r="S953" s="3"/>
-      <c r="T953" s="3"/>
-      <c r="U953" s="3"/>
-      <c r="V953" s="3"/>
-      <c r="W953" s="3"/>
-      <c r="X953" s="3"/>
-      <c r="Y953" s="3"/>
-      <c r="Z953" s="3"/>
-      <c r="AA953" s="3"/>
-      <c r="AB953" s="3"/>
-      <c r="AC953" s="3"/>
-      <c r="AD953" s="3"/>
-      <c r="AE953" s="3"/>
-    </row>
-    <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="3"/>
-      <c r="B954" s="3"/>
-      <c r="C954" s="3"/>
-      <c r="D954" s="3"/>
-      <c r="E954" s="3"/>
-      <c r="F954" s="3"/>
-      <c r="G954" s="3"/>
-      <c r="H954" s="3"/>
-      <c r="I954" s="3"/>
-      <c r="J954" s="3"/>
-      <c r="K954" s="3"/>
-      <c r="L954" s="3"/>
-      <c r="M954" s="3"/>
-      <c r="N954" s="3"/>
-      <c r="O954" s="3"/>
-      <c r="P954" s="3"/>
-      <c r="Q954" s="3"/>
-      <c r="R954" s="3"/>
-      <c r="S954" s="3"/>
-      <c r="T954" s="3"/>
-      <c r="U954" s="3"/>
-      <c r="V954" s="3"/>
-      <c r="W954" s="3"/>
-      <c r="X954" s="3"/>
-      <c r="Y954" s="3"/>
-      <c r="Z954" s="3"/>
-      <c r="AA954" s="3"/>
-      <c r="AB954" s="3"/>
-      <c r="AC954" s="3"/>
-      <c r="AD954" s="3"/>
-      <c r="AE954" s="3"/>
-    </row>
-    <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="3"/>
-      <c r="B955" s="3"/>
-      <c r="C955" s="3"/>
-      <c r="D955" s="3"/>
-      <c r="E955" s="3"/>
-      <c r="F955" s="3"/>
-      <c r="G955" s="3"/>
-      <c r="H955" s="3"/>
-      <c r="I955" s="3"/>
-      <c r="J955" s="3"/>
-      <c r="K955" s="3"/>
-      <c r="L955" s="3"/>
-      <c r="M955" s="3"/>
-      <c r="N955" s="3"/>
-      <c r="O955" s="3"/>
-      <c r="P955" s="3"/>
-      <c r="Q955" s="3"/>
-      <c r="R955" s="3"/>
-      <c r="S955" s="3"/>
-      <c r="T955" s="3"/>
-      <c r="U955" s="3"/>
-      <c r="V955" s="3"/>
-      <c r="W955" s="3"/>
-      <c r="X955" s="3"/>
-      <c r="Y955" s="3"/>
-      <c r="Z955" s="3"/>
-      <c r="AA955" s="3"/>
-      <c r="AB955" s="3"/>
-      <c r="AC955" s="3"/>
-      <c r="AD955" s="3"/>
-      <c r="AE955" s="3"/>
-    </row>
-    <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="3"/>
-      <c r="B956" s="3"/>
-      <c r="C956" s="3"/>
-      <c r="D956" s="3"/>
-      <c r="E956" s="3"/>
-      <c r="F956" s="3"/>
-      <c r="G956" s="3"/>
-      <c r="H956" s="3"/>
-      <c r="I956" s="3"/>
-      <c r="J956" s="3"/>
-      <c r="K956" s="3"/>
-      <c r="L956" s="3"/>
-      <c r="M956" s="3"/>
-      <c r="N956" s="3"/>
-      <c r="O956" s="3"/>
-      <c r="P956" s="3"/>
-      <c r="Q956" s="3"/>
-      <c r="R956" s="3"/>
-      <c r="S956" s="3"/>
-      <c r="T956" s="3"/>
-      <c r="U956" s="3"/>
-      <c r="V956" s="3"/>
-      <c r="W956" s="3"/>
-      <c r="X956" s="3"/>
-      <c r="Y956" s="3"/>
-      <c r="Z956" s="3"/>
-      <c r="AA956" s="3"/>
-      <c r="AB956" s="3"/>
-      <c r="AC956" s="3"/>
-      <c r="AD956" s="3"/>
-      <c r="AE956" s="3"/>
-    </row>
-    <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="3"/>
-      <c r="B957" s="3"/>
-      <c r="C957" s="3"/>
-      <c r="D957" s="3"/>
-      <c r="E957" s="3"/>
-      <c r="F957" s="3"/>
-      <c r="G957" s="3"/>
-      <c r="H957" s="3"/>
-      <c r="I957" s="3"/>
-      <c r="J957" s="3"/>
-      <c r="K957" s="3"/>
-      <c r="L957" s="3"/>
-      <c r="M957" s="3"/>
-      <c r="N957" s="3"/>
-      <c r="O957" s="3"/>
-      <c r="P957" s="3"/>
-      <c r="Q957" s="3"/>
-      <c r="R957" s="3"/>
-      <c r="S957" s="3"/>
-      <c r="T957" s="3"/>
-      <c r="U957" s="3"/>
-      <c r="V957" s="3"/>
-      <c r="W957" s="3"/>
-      <c r="X957" s="3"/>
-      <c r="Y957" s="3"/>
-      <c r="Z957" s="3"/>
-      <c r="AA957" s="3"/>
-      <c r="AB957" s="3"/>
-      <c r="AC957" s="3"/>
-      <c r="AD957" s="3"/>
-      <c r="AE957" s="3"/>
-    </row>
-    <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="3"/>
-      <c r="B958" s="3"/>
-      <c r="C958" s="3"/>
-      <c r="D958" s="3"/>
-      <c r="E958" s="3"/>
-      <c r="F958" s="3"/>
-      <c r="G958" s="3"/>
-      <c r="H958" s="3"/>
-      <c r="I958" s="3"/>
-      <c r="J958" s="3"/>
-      <c r="K958" s="3"/>
-      <c r="L958" s="3"/>
-      <c r="M958" s="3"/>
-      <c r="N958" s="3"/>
-      <c r="O958" s="3"/>
-      <c r="P958" s="3"/>
-      <c r="Q958" s="3"/>
-      <c r="R958" s="3"/>
-      <c r="S958" s="3"/>
-      <c r="T958" s="3"/>
-      <c r="U958" s="3"/>
-      <c r="V958" s="3"/>
-      <c r="W958" s="3"/>
-      <c r="X958" s="3"/>
-      <c r="Y958" s="3"/>
-      <c r="Z958" s="3"/>
-      <c r="AA958" s="3"/>
-      <c r="AB958" s="3"/>
-      <c r="AC958" s="3"/>
-      <c r="AD958" s="3"/>
-      <c r="AE958" s="3"/>
-    </row>
-    <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="3"/>
-      <c r="B959" s="3"/>
-      <c r="C959" s="3"/>
-      <c r="D959" s="3"/>
-      <c r="E959" s="3"/>
-      <c r="F959" s="3"/>
-      <c r="G959" s="3"/>
-      <c r="H959" s="3"/>
-      <c r="I959" s="3"/>
-      <c r="J959" s="3"/>
-      <c r="K959" s="3"/>
-      <c r="L959" s="3"/>
-      <c r="M959" s="3"/>
-      <c r="N959" s="3"/>
-      <c r="O959" s="3"/>
-      <c r="P959" s="3"/>
-      <c r="Q959" s="3"/>
-      <c r="R959" s="3"/>
-      <c r="S959" s="3"/>
-      <c r="T959" s="3"/>
-      <c r="U959" s="3"/>
-      <c r="V959" s="3"/>
-      <c r="W959" s="3"/>
-      <c r="X959" s="3"/>
-      <c r="Y959" s="3"/>
-      <c r="Z959" s="3"/>
-      <c r="AA959" s="3"/>
-      <c r="AB959" s="3"/>
-      <c r="AC959" s="3"/>
-      <c r="AD959" s="3"/>
-      <c r="AE959" s="3"/>
-    </row>
-    <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="3"/>
-      <c r="B960" s="3"/>
-      <c r="C960" s="3"/>
-      <c r="D960" s="3"/>
-      <c r="E960" s="3"/>
-      <c r="F960" s="3"/>
-      <c r="G960" s="3"/>
-      <c r="H960" s="3"/>
-      <c r="I960" s="3"/>
-      <c r="J960" s="3"/>
-      <c r="K960" s="3"/>
-      <c r="L960" s="3"/>
-      <c r="M960" s="3"/>
-      <c r="N960" s="3"/>
-      <c r="O960" s="3"/>
-      <c r="P960" s="3"/>
-      <c r="Q960" s="3"/>
-      <c r="R960" s="3"/>
-      <c r="S960" s="3"/>
-      <c r="T960" s="3"/>
-      <c r="U960" s="3"/>
-      <c r="V960" s="3"/>
-      <c r="W960" s="3"/>
-      <c r="X960" s="3"/>
-      <c r="Y960" s="3"/>
-      <c r="Z960" s="3"/>
-      <c r="AA960" s="3"/>
-      <c r="AB960" s="3"/>
-      <c r="AC960" s="3"/>
-      <c r="AD960" s="3"/>
-      <c r="AE960" s="3"/>
-    </row>
-    <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="3"/>
-      <c r="B961" s="3"/>
-      <c r="C961" s="3"/>
-      <c r="D961" s="3"/>
-      <c r="E961" s="3"/>
-      <c r="F961" s="3"/>
-      <c r="G961" s="3"/>
-      <c r="H961" s="3"/>
-      <c r="I961" s="3"/>
-      <c r="J961" s="3"/>
-      <c r="K961" s="3"/>
-      <c r="L961" s="3"/>
-      <c r="M961" s="3"/>
-      <c r="N961" s="3"/>
-      <c r="O961" s="3"/>
-      <c r="P961" s="3"/>
-      <c r="Q961" s="3"/>
-      <c r="R961" s="3"/>
-      <c r="S961" s="3"/>
-      <c r="T961" s="3"/>
-      <c r="U961" s="3"/>
-      <c r="V961" s="3"/>
-      <c r="W961" s="3"/>
-      <c r="X961" s="3"/>
-      <c r="Y961" s="3"/>
-      <c r="Z961" s="3"/>
-      <c r="AA961" s="3"/>
-      <c r="AB961" s="3"/>
-      <c r="AC961" s="3"/>
-      <c r="AD961" s="3"/>
-      <c r="AE961" s="3"/>
-    </row>
-    <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="3"/>
-      <c r="B962" s="3"/>
-      <c r="C962" s="3"/>
-      <c r="D962" s="3"/>
-      <c r="E962" s="3"/>
-      <c r="F962" s="3"/>
-      <c r="G962" s="3"/>
-      <c r="H962" s="3"/>
-      <c r="I962" s="3"/>
-      <c r="J962" s="3"/>
-      <c r="K962" s="3"/>
-      <c r="L962" s="3"/>
-      <c r="M962" s="3"/>
-      <c r="N962" s="3"/>
-      <c r="O962" s="3"/>
-      <c r="P962" s="3"/>
-      <c r="Q962" s="3"/>
-      <c r="R962" s="3"/>
-      <c r="S962" s="3"/>
-      <c r="T962" s="3"/>
-      <c r="U962" s="3"/>
-      <c r="V962" s="3"/>
-      <c r="W962" s="3"/>
-      <c r="X962" s="3"/>
-      <c r="Y962" s="3"/>
-      <c r="Z962" s="3"/>
-      <c r="AA962" s="3"/>
-      <c r="AB962" s="3"/>
-      <c r="AC962" s="3"/>
-      <c r="AD962" s="3"/>
-      <c r="AE962" s="3"/>
-    </row>
-    <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="3"/>
-      <c r="B963" s="3"/>
-      <c r="C963" s="3"/>
-      <c r="D963" s="3"/>
-      <c r="E963" s="3"/>
-      <c r="F963" s="3"/>
-      <c r="G963" s="3"/>
-      <c r="H963" s="3"/>
-      <c r="I963" s="3"/>
-      <c r="J963" s="3"/>
-      <c r="K963" s="3"/>
-      <c r="L963" s="3"/>
-      <c r="M963" s="3"/>
-      <c r="N963" s="3"/>
-      <c r="O963" s="3"/>
-      <c r="P963" s="3"/>
-      <c r="Q963" s="3"/>
-      <c r="R963" s="3"/>
-      <c r="S963" s="3"/>
-      <c r="T963" s="3"/>
-      <c r="U963" s="3"/>
-      <c r="V963" s="3"/>
-      <c r="W963" s="3"/>
-      <c r="X963" s="3"/>
-      <c r="Y963" s="3"/>
-      <c r="Z963" s="3"/>
-      <c r="AA963" s="3"/>
-      <c r="AB963" s="3"/>
-      <c r="AC963" s="3"/>
-      <c r="AD963" s="3"/>
-      <c r="AE963" s="3"/>
-    </row>
-    <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="3"/>
-      <c r="B964" s="3"/>
-      <c r="C964" s="3"/>
-      <c r="D964" s="3"/>
-      <c r="E964" s="3"/>
-      <c r="F964" s="3"/>
-      <c r="G964" s="3"/>
-      <c r="H964" s="3"/>
-      <c r="I964" s="3"/>
-      <c r="J964" s="3"/>
-      <c r="K964" s="3"/>
-      <c r="L964" s="3"/>
-      <c r="M964" s="3"/>
-      <c r="N964" s="3"/>
-      <c r="O964" s="3"/>
-      <c r="P964" s="3"/>
-      <c r="Q964" s="3"/>
-      <c r="R964" s="3"/>
-      <c r="S964" s="3"/>
-      <c r="T964" s="3"/>
-      <c r="U964" s="3"/>
-      <c r="V964" s="3"/>
-      <c r="W964" s="3"/>
-      <c r="X964" s="3"/>
-      <c r="Y964" s="3"/>
-      <c r="Z964" s="3"/>
-      <c r="AA964" s="3"/>
-      <c r="AB964" s="3"/>
-      <c r="AC964" s="3"/>
-      <c r="AD964" s="3"/>
-      <c r="AE964" s="3"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="G2"/>
-    <hyperlink r:id="rId2" ref="J2"/>
+    <hyperlink r:id="rId2" ref="K2"/>
     <hyperlink r:id="rId3" ref="G3"/>
-    <hyperlink r:id="rId4" ref="J3"/>
+    <hyperlink r:id="rId4" ref="K3"/>
     <hyperlink r:id="rId5" ref="G4"/>
-    <hyperlink r:id="rId6" ref="J4"/>
+    <hyperlink r:id="rId6" ref="K4"/>
     <hyperlink r:id="rId7" ref="G5"/>
-    <hyperlink r:id="rId8" ref="J5"/>
+    <hyperlink r:id="rId8" ref="K5"/>
     <hyperlink r:id="rId9" ref="G6"/>
-    <hyperlink r:id="rId10" ref="J6"/>
+    <hyperlink r:id="rId10" ref="K6"/>
     <hyperlink r:id="rId11" ref="G7"/>
-    <hyperlink r:id="rId12" ref="J7"/>
-    <hyperlink r:id="rId13" ref="G8"/>
-    <hyperlink r:id="rId14" ref="J8"/>
-    <hyperlink r:id="rId15" ref="G9"/>
-    <hyperlink r:id="rId16" ref="J9"/>
-    <hyperlink r:id="rId17" ref="G10"/>
-    <hyperlink r:id="rId18" ref="J10"/>
-    <hyperlink r:id="rId19" ref="G11"/>
-    <hyperlink r:id="rId20" ref="J11"/>
-    <hyperlink r:id="rId21" ref="G12"/>
-    <hyperlink r:id="rId22" ref="J12"/>
-    <hyperlink r:id="rId23" ref="G13"/>
-    <hyperlink r:id="rId24" ref="J13"/>
-    <hyperlink r:id="rId25" ref="G14"/>
-    <hyperlink r:id="rId26" ref="J14"/>
-    <hyperlink r:id="rId27" ref="G15"/>
-    <hyperlink r:id="rId28" ref="J15"/>
-    <hyperlink r:id="rId29" ref="G16"/>
-    <hyperlink r:id="rId30" ref="J16"/>
-    <hyperlink r:id="rId31" ref="G17"/>
-    <hyperlink r:id="rId32" ref="J17"/>
-    <hyperlink r:id="rId33" ref="G18"/>
-    <hyperlink r:id="rId34" ref="G19"/>
-    <hyperlink r:id="rId35" ref="J19"/>
-    <hyperlink r:id="rId36" ref="G20"/>
-    <hyperlink r:id="rId37" ref="G21"/>
-    <hyperlink r:id="rId38" ref="J21"/>
-    <hyperlink r:id="rId39" ref="G22"/>
-    <hyperlink r:id="rId40" ref="J22"/>
-    <hyperlink r:id="rId41" ref="G23"/>
-    <hyperlink r:id="rId42" ref="G24"/>
-    <hyperlink r:id="rId43" ref="J24"/>
-    <hyperlink r:id="rId44" ref="G25"/>
-    <hyperlink r:id="rId45" ref="J25"/>
+    <hyperlink r:id="rId12" ref="K7"/>
+    <hyperlink r:id="rId13" ref="L7"/>
+    <hyperlink r:id="rId14" ref="G8"/>
+    <hyperlink r:id="rId15" ref="K8"/>
+    <hyperlink r:id="rId16" ref="G9"/>
+    <hyperlink r:id="rId17" ref="K9"/>
+    <hyperlink r:id="rId18" ref="G10"/>
+    <hyperlink r:id="rId19" ref="K10"/>
+    <hyperlink r:id="rId20" ref="G11"/>
+    <hyperlink r:id="rId21" ref="K11"/>
+    <hyperlink r:id="rId22" ref="G12"/>
+    <hyperlink r:id="rId23" ref="K12"/>
+    <hyperlink r:id="rId24" ref="G13"/>
+    <hyperlink r:id="rId25" ref="K13"/>
+    <hyperlink r:id="rId26" ref="G14"/>
+    <hyperlink r:id="rId27" ref="K14"/>
+    <hyperlink r:id="rId28" ref="G15"/>
+    <hyperlink r:id="rId29" ref="K15"/>
+    <hyperlink r:id="rId30" ref="G16"/>
+    <hyperlink r:id="rId31" ref="K16"/>
+    <hyperlink r:id="rId32" ref="G17"/>
+    <hyperlink r:id="rId33" ref="K17"/>
+    <hyperlink r:id="rId34" ref="G18"/>
+    <hyperlink r:id="rId35" ref="K18"/>
+    <hyperlink r:id="rId36" ref="G19"/>
+    <hyperlink r:id="rId37" ref="K19"/>
+    <hyperlink r:id="rId38" ref="G20"/>
+    <hyperlink r:id="rId39" ref="K20"/>
+    <hyperlink r:id="rId40" ref="G21"/>
+    <hyperlink r:id="rId41" ref="K21"/>
+    <hyperlink r:id="rId42" ref="G22"/>
+    <hyperlink r:id="rId43" ref="K22"/>
+    <hyperlink r:id="rId44" ref="G23"/>
+    <hyperlink r:id="rId45" ref="K23"/>
+    <hyperlink r:id="rId46" ref="G24"/>
+    <hyperlink r:id="rId47" ref="K24"/>
+    <hyperlink r:id="rId48" ref="G25"/>
+    <hyperlink r:id="rId49" ref="K25"/>
+    <hyperlink r:id="rId50" ref="G26"/>
+    <hyperlink r:id="rId51" ref="G27"/>
+    <hyperlink r:id="rId52" ref="K27"/>
+    <hyperlink r:id="rId53" ref="G28"/>
+    <hyperlink r:id="rId54" ref="K28"/>
+    <hyperlink r:id="rId55" ref="G29"/>
+    <hyperlink r:id="rId56" ref="K29"/>
+    <hyperlink r:id="rId57" ref="G30"/>
+    <hyperlink r:id="rId58" ref="K30"/>
   </hyperlinks>
-  <drawing r:id="rId46"/>
+  <drawing r:id="rId59"/>
 </worksheet>
 </file>